--- a/research/traditional_assets/database/data/south_africa/south_africa_electrical_equipment.xlsx
+++ b/research/traditional_assets/database/data/south_africa/south_africa_electrical_equipment.xlsx
@@ -1278,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1415,22 +1415,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.1376988794247934</v>
+        <v>0.1373599424503464</v>
       </c>
       <c r="C2">
-        <v>37.92321431051101</v>
+        <v>37.65023606637238</v>
       </c>
       <c r="D2">
-        <v>37.92321431051101</v>
+        <v>38.04023606637238</v>
       </c>
       <c r="E2">
-        <v>-17.8</v>
+        <v>-17.41</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>0.39</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -1451,28 +1451,28 @@
         <v>8.31</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.019617</v>
       </c>
       <c r="N2">
-        <v>8.31</v>
+        <v>8.290383</v>
       </c>
       <c r="O2">
-        <v>2.2437</v>
+        <v>2.23840341</v>
       </c>
       <c r="P2">
-        <v>6.0663</v>
+        <v>6.05197959</v>
       </c>
       <c r="Q2">
-        <v>6.9063</v>
+        <v>6.89197959</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.1376988794247934</v>
+        <v>0.1383765176266126</v>
       </c>
       <c r="T2">
-        <v>1.100924895422504</v>
+        <v>1.109042826469559</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>423.6121731151553</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1497,22 +1497,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1373599424503464</v>
+        <v>0.1370210054758995</v>
       </c>
       <c r="C3">
-        <v>37.65023606637238</v>
+        <v>37.37798225865114</v>
       </c>
       <c r="D3">
-        <v>38.04023606637238</v>
+        <v>38.15798225865115</v>
       </c>
       <c r="E3">
-        <v>-17.41</v>
+        <v>-17.02</v>
       </c>
       <c r="F3">
-        <v>0.39</v>
+        <v>0.78</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -1533,28 +1533,28 @@
         <v>8.31</v>
       </c>
       <c r="M3">
-        <v>0.019617</v>
+        <v>0.039234</v>
       </c>
       <c r="N3">
-        <v>8.290383</v>
+        <v>8.270766</v>
       </c>
       <c r="O3">
-        <v>2.23840341</v>
+        <v>2.23310682</v>
       </c>
       <c r="P3">
-        <v>6.05197959</v>
+        <v>6.03765918</v>
       </c>
       <c r="Q3">
-        <v>6.89197959</v>
+        <v>6.87765918</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1383765176266126</v>
+        <v>0.1390679851794893</v>
       </c>
       <c r="T3">
-        <v>1.109042826469559</v>
+        <v>1.117326429578799</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>423.6121731151553</v>
+        <v>211.8060865575776</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1579,22 +1579,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1370210054758995</v>
+        <v>0.1366820685014526</v>
       </c>
       <c r="C4">
-        <v>37.37798225865114</v>
+        <v>37.10645963529267</v>
       </c>
       <c r="D4">
-        <v>38.15798225865115</v>
+        <v>38.27645963529267</v>
       </c>
       <c r="E4">
-        <v>-17.02</v>
+        <v>-16.63</v>
       </c>
       <c r="F4">
-        <v>0.78</v>
+        <v>1.17</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -1615,28 +1615,28 @@
         <v>8.31</v>
       </c>
       <c r="M4">
-        <v>0.039234</v>
+        <v>0.05885099999999999</v>
       </c>
       <c r="N4">
-        <v>8.270766</v>
+        <v>8.251149</v>
       </c>
       <c r="O4">
-        <v>2.23310682</v>
+        <v>2.22781023</v>
       </c>
       <c r="P4">
-        <v>6.03765918</v>
+        <v>6.02333877</v>
       </c>
       <c r="Q4">
-        <v>6.87765918</v>
+        <v>6.863338769999999</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1390679851794893</v>
+        <v>0.1397737097953119</v>
       </c>
       <c r="T4">
-        <v>1.117326429578799</v>
+        <v>1.125780828628435</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>211.8060865575776</v>
+        <v>141.2040577050518</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1661,22 +1661,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1366820685014526</v>
+        <v>0.1363431315270056</v>
       </c>
       <c r="C5">
-        <v>37.10645963529267</v>
+        <v>36.83567502831055</v>
       </c>
       <c r="D5">
-        <v>38.27645963529267</v>
+        <v>38.39567502831055</v>
       </c>
       <c r="E5">
-        <v>-16.63</v>
+        <v>-16.24</v>
       </c>
       <c r="F5">
-        <v>1.17</v>
+        <v>1.56</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -1697,28 +1697,28 @@
         <v>8.31</v>
       </c>
       <c r="M5">
-        <v>0.05885099999999999</v>
+        <v>0.078468</v>
       </c>
       <c r="N5">
-        <v>8.251149</v>
+        <v>8.231532</v>
       </c>
       <c r="O5">
-        <v>2.22781023</v>
+        <v>2.22251364</v>
       </c>
       <c r="P5">
-        <v>6.02333877</v>
+        <v>6.00901836</v>
       </c>
       <c r="Q5">
-        <v>6.863338769999999</v>
+        <v>6.84901836</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1397737097953119</v>
+        <v>0.1404941370072975</v>
       </c>
       <c r="T5">
-        <v>1.125780828628435</v>
+        <v>1.134411360991606</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>141.2040577050518</v>
+        <v>105.9030432787888</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1363431315270056</v>
+        <v>0.1360041945525587</v>
       </c>
       <c r="C6">
-        <v>36.83567502831055</v>
+        <v>36.56563535509996</v>
       </c>
       <c r="D6">
-        <v>38.39567502831055</v>
+        <v>38.51563535509997</v>
       </c>
       <c r="E6">
-        <v>-16.24</v>
+        <v>-15.85</v>
       </c>
       <c r="F6">
-        <v>1.56</v>
+        <v>1.95</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -1779,28 +1779,28 @@
         <v>8.31</v>
       </c>
       <c r="M6">
-        <v>0.078468</v>
+        <v>0.09808500000000001</v>
       </c>
       <c r="N6">
-        <v>8.231532</v>
+        <v>8.211915000000001</v>
       </c>
       <c r="O6">
-        <v>2.22251364</v>
+        <v>2.21721705</v>
       </c>
       <c r="P6">
-        <v>6.00901836</v>
+        <v>5.994697950000001</v>
       </c>
       <c r="Q6">
-        <v>6.84901836</v>
+        <v>6.834697950000001</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1404941370072975</v>
+        <v>0.1412297311079565</v>
       </c>
       <c r="T6">
-        <v>1.134411360991606</v>
+        <v>1.143223588772948</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>105.9030432787888</v>
+        <v>84.72243462303105</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1825,22 +1825,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.1360041945525587</v>
+        <v>0.1356652575781117</v>
       </c>
       <c r="C7">
-        <v>36.56563535509996</v>
+        <v>36.2963476197756</v>
       </c>
       <c r="D7">
-        <v>38.51563535509997</v>
+        <v>38.63634761977561</v>
       </c>
       <c r="E7">
-        <v>-15.85</v>
+        <v>-15.46</v>
       </c>
       <c r="F7">
-        <v>1.95</v>
+        <v>2.34</v>
       </c>
       <c r="G7">
         <v>0</v>
@@ -1861,28 +1861,28 @@
         <v>8.31</v>
       </c>
       <c r="M7">
-        <v>0.09808500000000001</v>
+        <v>0.117702</v>
       </c>
       <c r="N7">
-        <v>8.211915000000001</v>
+        <v>8.192298000000001</v>
       </c>
       <c r="O7">
-        <v>2.21721705</v>
+        <v>2.21192046</v>
       </c>
       <c r="P7">
-        <v>5.994697950000001</v>
+        <v>5.980377540000001</v>
       </c>
       <c r="Q7">
-        <v>6.834697950000001</v>
+        <v>6.820377540000001</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1412297311079565</v>
+        <v>0.1419809761469274</v>
       </c>
       <c r="T7">
-        <v>1.143223588772948</v>
+        <v>1.152223310762404</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>84.72243462303105</v>
+        <v>70.60202885252588</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1907,22 +1907,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1356652575781117</v>
+        <v>0.1353263206036648</v>
       </c>
       <c r="C8">
-        <v>36.2963476197756</v>
+        <v>36.02781891453495</v>
       </c>
       <c r="D8">
-        <v>38.63634761977561</v>
+        <v>38.75781891453495</v>
       </c>
       <c r="E8">
-        <v>-15.46</v>
+        <v>-15.07</v>
       </c>
       <c r="F8">
-        <v>2.34</v>
+        <v>2.73</v>
       </c>
       <c r="G8">
         <v>0</v>
@@ -1943,28 +1943,28 @@
         <v>8.31</v>
       </c>
       <c r="M8">
-        <v>0.117702</v>
+        <v>0.137319</v>
       </c>
       <c r="N8">
-        <v>8.192298000000001</v>
+        <v>8.172681000000001</v>
       </c>
       <c r="O8">
-        <v>2.21192046</v>
+        <v>2.20662387</v>
       </c>
       <c r="P8">
-        <v>5.980377540000001</v>
+        <v>5.96605713</v>
       </c>
       <c r="Q8">
-        <v>6.820377540000001</v>
+        <v>6.80605713</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1419809761469274</v>
+        <v>0.1427483769931879</v>
       </c>
       <c r="T8">
-        <v>1.152223310762404</v>
+        <v>1.161416575160235</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>70.60202885252589</v>
+        <v>60.51602473073648</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1989,22 +1989,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1353263206036648</v>
+        <v>0.1349873836292179</v>
       </c>
       <c r="C9">
-        <v>36.02781891453495</v>
+        <v>35.76005642104715</v>
       </c>
       <c r="D9">
-        <v>38.75781891453495</v>
+        <v>38.88005642104715</v>
       </c>
       <c r="E9">
-        <v>-15.07</v>
+        <v>-14.68</v>
       </c>
       <c r="F9">
-        <v>2.73</v>
+        <v>3.12</v>
       </c>
       <c r="G9">
         <v>0</v>
@@ -2025,28 +2025,28 @@
         <v>8.31</v>
       </c>
       <c r="M9">
-        <v>0.137319</v>
+        <v>0.156936</v>
       </c>
       <c r="N9">
-        <v>8.172681000000001</v>
+        <v>8.153064000000001</v>
       </c>
       <c r="O9">
-        <v>2.20662387</v>
+        <v>2.20132728</v>
       </c>
       <c r="P9">
-        <v>5.96605713</v>
+        <v>5.95173672</v>
       </c>
       <c r="Q9">
-        <v>6.80605713</v>
+        <v>6.79173672</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1427483769931879</v>
+        <v>0.1435324604665411</v>
       </c>
       <c r="T9">
-        <v>1.161416575160235</v>
+        <v>1.170809693131933</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>60.51602473073645</v>
+        <v>52.95152163939441</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2071,22 +2071,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1349873836292179</v>
+        <v>0.1346484466547709</v>
       </c>
       <c r="C10">
-        <v>35.76005642104715</v>
+        <v>35.49306741186859</v>
       </c>
       <c r="D10">
-        <v>38.88005642104715</v>
+        <v>39.00306741186859</v>
       </c>
       <c r="E10">
-        <v>-14.68</v>
+        <v>-14.29</v>
       </c>
       <c r="F10">
-        <v>3.12</v>
+        <v>3.51</v>
       </c>
       <c r="G10">
         <v>0</v>
@@ -2107,28 +2107,28 @@
         <v>8.31</v>
       </c>
       <c r="M10">
-        <v>0.156936</v>
+        <v>0.176553</v>
       </c>
       <c r="N10">
-        <v>8.153064000000001</v>
+        <v>8.133447</v>
       </c>
       <c r="O10">
-        <v>2.20132728</v>
+        <v>2.19603069</v>
       </c>
       <c r="P10">
-        <v>5.95173672</v>
+        <v>5.93741631</v>
       </c>
       <c r="Q10">
-        <v>6.79173672</v>
+        <v>6.77741631</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1435324604665411</v>
+        <v>0.1443337765437043</v>
       </c>
       <c r="T10">
-        <v>1.170809693131933</v>
+        <v>1.180409253256854</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>52.95152163939441</v>
+        <v>47.06801923501725</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2153,22 +2153,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1346484466547709</v>
+        <v>0.134309509680324</v>
       </c>
       <c r="C11">
-        <v>35.49306741186859</v>
+        <v>35.22685925188504</v>
       </c>
       <c r="D11">
-        <v>39.00306741186859</v>
+        <v>39.12685925188504</v>
       </c>
       <c r="E11">
-        <v>-14.29</v>
+        <v>-13.9</v>
       </c>
       <c r="F11">
-        <v>3.51</v>
+        <v>3.899999999999999</v>
       </c>
       <c r="G11">
         <v>0</v>
@@ -2189,28 +2189,28 @@
         <v>8.31</v>
       </c>
       <c r="M11">
-        <v>0.176553</v>
+        <v>0.19617</v>
       </c>
       <c r="N11">
-        <v>8.133447</v>
+        <v>8.11383</v>
       </c>
       <c r="O11">
-        <v>2.19603069</v>
+        <v>2.1907341</v>
       </c>
       <c r="P11">
-        <v>5.93741631</v>
+        <v>5.9230959</v>
       </c>
       <c r="Q11">
-        <v>6.77741631</v>
+        <v>6.7630959</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1443337765437043</v>
+        <v>0.1451528996448044</v>
       </c>
       <c r="T11">
-        <v>1.180409253256854</v>
+        <v>1.190222136940108</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2227,7 +2227,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>47.06801923501725</v>
+        <v>42.36121731151553</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2235,22 +2235,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.134309509680324</v>
+        <v>0.133970572705877</v>
       </c>
       <c r="C12">
-        <v>35.22685925188504</v>
+        <v>34.9614393997817</v>
       </c>
       <c r="D12">
-        <v>39.12685925188504</v>
+        <v>39.2514393997817</v>
       </c>
       <c r="E12">
-        <v>-13.9</v>
+        <v>-13.51</v>
       </c>
       <c r="F12">
-        <v>3.9</v>
+        <v>4.29</v>
       </c>
       <c r="G12">
         <v>0</v>
@@ -2271,28 +2271,28 @@
         <v>8.31</v>
       </c>
       <c r="M12">
-        <v>0.19617</v>
+        <v>0.215787</v>
       </c>
       <c r="N12">
-        <v>8.11383</v>
+        <v>8.094213</v>
       </c>
       <c r="O12">
-        <v>2.1907341</v>
+        <v>2.18543751</v>
       </c>
       <c r="P12">
-        <v>5.9230959</v>
+        <v>5.90877549</v>
       </c>
       <c r="Q12">
-        <v>6.7630959</v>
+        <v>6.74877549</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1451528996448044</v>
+        <v>0.1459904300066034</v>
       </c>
       <c r="T12">
-        <v>1.190222136940108</v>
+        <v>1.200255534863434</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>42.36121731151552</v>
+        <v>38.51019755592321</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2317,22 +2317,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.133970572705877</v>
+        <v>0.1336316357314301</v>
       </c>
       <c r="C13">
-        <v>34.9614393997817</v>
+        <v>34.6968154095411</v>
       </c>
       <c r="D13">
-        <v>39.2514393997817</v>
+        <v>39.37681540954109</v>
       </c>
       <c r="E13">
-        <v>-13.51</v>
+        <v>-13.12</v>
       </c>
       <c r="F13">
-        <v>4.29</v>
+        <v>4.68</v>
       </c>
       <c r="G13">
         <v>0</v>
@@ -2353,28 +2353,28 @@
         <v>8.31</v>
       </c>
       <c r="M13">
-        <v>0.215787</v>
+        <v>0.235404</v>
       </c>
       <c r="N13">
-        <v>8.094213</v>
+        <v>8.074596</v>
       </c>
       <c r="O13">
-        <v>2.18543751</v>
+        <v>2.18014092</v>
       </c>
       <c r="P13">
-        <v>5.90877549</v>
+        <v>5.89445508</v>
       </c>
       <c r="Q13">
-        <v>6.74877549</v>
+        <v>6.73445508</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1459904300066034</v>
+        <v>0.1468469951493524</v>
       </c>
       <c r="T13">
-        <v>1.200255534863434</v>
+        <v>1.210516964557745</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2391,7 +2391,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>38.51019755592321</v>
+        <v>35.30101442626294</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2399,22 +2399,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.1336316357314301</v>
+        <v>0.1332926987569831</v>
       </c>
       <c r="C14">
-        <v>34.6968154095411</v>
+        <v>34.43299493197016</v>
       </c>
       <c r="D14">
-        <v>39.37681540954109</v>
+        <v>39.50299493197016</v>
       </c>
       <c r="E14">
-        <v>-13.12</v>
+        <v>-12.73</v>
       </c>
       <c r="F14">
-        <v>4.68</v>
+        <v>5.07</v>
       </c>
       <c r="G14">
         <v>0</v>
@@ -2435,28 +2435,28 @@
         <v>8.31</v>
       </c>
       <c r="M14">
-        <v>0.235404</v>
+        <v>0.255021</v>
       </c>
       <c r="N14">
-        <v>8.074596</v>
+        <v>8.054979000000001</v>
       </c>
       <c r="O14">
-        <v>2.18014092</v>
+        <v>2.17484433</v>
       </c>
       <c r="P14">
-        <v>5.89445508</v>
+        <v>5.88013467</v>
       </c>
       <c r="Q14">
-        <v>6.73445508</v>
+        <v>6.72013467</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1468469951493524</v>
+        <v>0.1477232514448082</v>
       </c>
       <c r="T14">
-        <v>1.210516964557745</v>
+        <v>1.221014289187557</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2473,7 +2473,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>35.30101442626294</v>
+        <v>32.58555177808887</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2481,22 +2481,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1332926987569831</v>
+        <v>0.1329537617825362</v>
       </c>
       <c r="C15">
-        <v>34.43299493197016</v>
+        <v>34.16998571625626</v>
       </c>
       <c r="D15">
-        <v>39.50299493197016</v>
+        <v>39.62998571625626</v>
       </c>
       <c r="E15">
-        <v>-12.73</v>
+        <v>-12.34</v>
       </c>
       <c r="F15">
-        <v>5.07</v>
+        <v>5.460000000000001</v>
       </c>
       <c r="G15">
         <v>0</v>
@@ -2517,28 +2517,28 @@
         <v>8.31</v>
       </c>
       <c r="M15">
-        <v>0.255021</v>
+        <v>0.274638</v>
       </c>
       <c r="N15">
-        <v>8.054979000000001</v>
+        <v>8.035362000000001</v>
       </c>
       <c r="O15">
-        <v>2.17484433</v>
+        <v>2.169547740000001</v>
       </c>
       <c r="P15">
-        <v>5.88013467</v>
+        <v>5.865814260000001</v>
       </c>
       <c r="Q15">
-        <v>6.72013467</v>
+        <v>6.70581426</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1477232514448082</v>
+        <v>0.1486198857936467</v>
       </c>
       <c r="T15">
-        <v>1.221014289187557</v>
+        <v>1.231755737645969</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>32.58555177808887</v>
+        <v>30.25801236536823</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2563,22 +2563,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1329537617825362</v>
+        <v>0.1326148248080893</v>
       </c>
       <c r="C16">
-        <v>34.16998571625626</v>
+        <v>33.90779561155389</v>
       </c>
       <c r="D16">
-        <v>39.62998571625626</v>
+        <v>39.75779561155389</v>
       </c>
       <c r="E16">
-        <v>-12.34</v>
+        <v>-11.95</v>
       </c>
       <c r="F16">
-        <v>5.460000000000001</v>
+        <v>5.850000000000001</v>
       </c>
       <c r="G16">
         <v>0</v>
@@ -2599,28 +2599,28 @@
         <v>8.31</v>
       </c>
       <c r="M16">
-        <v>0.274638</v>
+        <v>0.294255</v>
       </c>
       <c r="N16">
-        <v>8.035362000000001</v>
+        <v>8.015745000000001</v>
       </c>
       <c r="O16">
-        <v>2.169547740000001</v>
+        <v>2.164251150000001</v>
       </c>
       <c r="P16">
-        <v>5.865814260000001</v>
+        <v>5.851493850000001</v>
       </c>
       <c r="Q16">
-        <v>6.70581426</v>
+        <v>6.691493850000001</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1486198857936467</v>
+        <v>0.1495376174212815</v>
       </c>
       <c r="T16">
-        <v>1.231755737645969</v>
+        <v>1.242749926068109</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2637,7 +2637,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>30.25801236536823</v>
+        <v>28.24081154101035</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2645,22 +2645,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1326148248080893</v>
+        <v>0.1322758878336423</v>
       </c>
       <c r="C17">
-        <v>33.90779561155389</v>
+        <v>33.64643256860173</v>
       </c>
       <c r="D17">
-        <v>39.75779561155389</v>
+        <v>39.88643256860173</v>
       </c>
       <c r="E17">
-        <v>-11.95</v>
+        <v>-11.56</v>
       </c>
       <c r="F17">
-        <v>5.85</v>
+        <v>6.24</v>
       </c>
       <c r="G17">
         <v>0</v>
@@ -2681,28 +2681,28 @@
         <v>8.31</v>
       </c>
       <c r="M17">
-        <v>0.294255</v>
+        <v>0.313872</v>
       </c>
       <c r="N17">
-        <v>8.015745000000001</v>
+        <v>7.996128000000001</v>
       </c>
       <c r="O17">
-        <v>2.164251150000001</v>
+        <v>2.15895456</v>
       </c>
       <c r="P17">
-        <v>5.851493850000001</v>
+        <v>5.837173440000001</v>
       </c>
       <c r="Q17">
-        <v>6.691493850000001</v>
+        <v>6.677173440000001</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1495376174212815</v>
+        <v>0.1504771998019551</v>
       </c>
       <c r="T17">
-        <v>1.242749926068109</v>
+        <v>1.254005880881253</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2719,7 +2719,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>28.24081154101035</v>
+        <v>26.4757608196972</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2727,22 +2727,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.1322758878336423</v>
+        <v>0.1319369508591954</v>
       </c>
       <c r="C18">
-        <v>33.64643256860173</v>
+        <v>33.38590464137146</v>
       </c>
       <c r="D18">
-        <v>39.88643256860173</v>
+        <v>40.01590464137146</v>
       </c>
       <c r="E18">
-        <v>-11.56</v>
+        <v>-11.17</v>
       </c>
       <c r="F18">
-        <v>6.24</v>
+        <v>6.630000000000001</v>
       </c>
       <c r="G18">
         <v>0</v>
@@ -2763,28 +2763,28 @@
         <v>8.31</v>
       </c>
       <c r="M18">
-        <v>0.313872</v>
+        <v>0.333489</v>
       </c>
       <c r="N18">
-        <v>7.996128000000001</v>
+        <v>7.976511</v>
       </c>
       <c r="O18">
-        <v>2.15895456</v>
+        <v>2.15365797</v>
       </c>
       <c r="P18">
-        <v>5.837173440000001</v>
+        <v>5.82285303</v>
       </c>
       <c r="Q18">
-        <v>6.677173440000001</v>
+        <v>6.66285303</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1504771998019551</v>
+        <v>0.1514394227219222</v>
       </c>
       <c r="T18">
-        <v>1.254005880881253</v>
+        <v>1.265533063521219</v>
       </c>
       <c r="U18">
         <v>0.0503</v>
@@ -2801,7 +2801,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>26.4757608196972</v>
+        <v>24.91836312442089</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1319369508591954</v>
+        <v>0.1315980138847484</v>
       </c>
       <c r="C19">
-        <v>33.38590464137146</v>
+        <v>33.12621998874862</v>
       </c>
       <c r="D19">
-        <v>40.01590464137146</v>
+        <v>40.14621998874863</v>
       </c>
       <c r="E19">
-        <v>-11.17</v>
+        <v>-10.78</v>
       </c>
       <c r="F19">
-        <v>6.630000000000001</v>
+        <v>7.02</v>
       </c>
       <c r="G19">
         <v>0</v>
@@ -2845,28 +2845,28 @@
         <v>8.31</v>
       </c>
       <c r="M19">
-        <v>0.333489</v>
+        <v>0.353106</v>
       </c>
       <c r="N19">
-        <v>7.976511</v>
+        <v>7.956894</v>
       </c>
       <c r="O19">
-        <v>2.15365797</v>
+        <v>2.14836138</v>
       </c>
       <c r="P19">
-        <v>5.82285303</v>
+        <v>5.808532619999999</v>
       </c>
       <c r="Q19">
-        <v>6.66285303</v>
+        <v>6.648532619999999</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1514394227219222</v>
+        <v>0.1524251144935956</v>
       </c>
       <c r="T19">
-        <v>1.265533063521219</v>
+        <v>1.277341396957281</v>
       </c>
       <c r="U19">
         <v>0.0503</v>
@@ -2883,7 +2883,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>24.91836312442089</v>
+        <v>23.53400961750862</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2891,22 +2891,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1315980138847484</v>
+        <v>0.1312590769103015</v>
       </c>
       <c r="C20">
-        <v>33.12621998874863</v>
+        <v>32.86738687624651</v>
       </c>
       <c r="D20">
-        <v>40.14621998874863</v>
+        <v>40.27738687624652</v>
       </c>
       <c r="E20">
-        <v>-10.78</v>
+        <v>-10.39</v>
       </c>
       <c r="F20">
-        <v>7.02</v>
+        <v>7.41</v>
       </c>
       <c r="G20">
         <v>0</v>
@@ -2927,28 +2927,28 @@
         <v>8.31</v>
       </c>
       <c r="M20">
-        <v>0.353106</v>
+        <v>0.372723</v>
       </c>
       <c r="N20">
-        <v>7.956894</v>
+        <v>7.937277000000001</v>
       </c>
       <c r="O20">
-        <v>2.14836138</v>
+        <v>2.14306479</v>
       </c>
       <c r="P20">
-        <v>5.808532619999999</v>
+        <v>5.79421221</v>
       </c>
       <c r="Q20">
-        <v>6.648532619999999</v>
+        <v>6.63421221</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1524251144935956</v>
+        <v>0.1534351443337055</v>
       </c>
       <c r="T20">
-        <v>1.277341396957281</v>
+        <v>1.289441294181889</v>
       </c>
       <c r="U20">
         <v>0.0503</v>
@@ -2965,7 +2965,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>23.53400961750863</v>
+        <v>22.29537753237659</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2973,22 +2973,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1312590769103015</v>
+        <v>0.1309201399358546</v>
       </c>
       <c r="C21">
-        <v>32.86738687624651</v>
+        <v>32.60941367775391</v>
       </c>
       <c r="D21">
-        <v>40.27738687624652</v>
+        <v>40.40941367775391</v>
       </c>
       <c r="E21">
-        <v>-10.39</v>
+        <v>-10</v>
       </c>
       <c r="F21">
-        <v>7.41</v>
+        <v>7.800000000000001</v>
       </c>
       <c r="G21">
         <v>0</v>
@@ -3009,28 +3009,28 @@
         <v>8.31</v>
       </c>
       <c r="M21">
-        <v>0.372723</v>
+        <v>0.39234</v>
       </c>
       <c r="N21">
-        <v>7.937277000000001</v>
+        <v>7.917660000000001</v>
       </c>
       <c r="O21">
-        <v>2.14306479</v>
+        <v>2.1377682</v>
       </c>
       <c r="P21">
-        <v>5.79421221</v>
+        <v>5.7798918</v>
       </c>
       <c r="Q21">
-        <v>6.63421221</v>
+        <v>6.6198918</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1534351443337055</v>
+        <v>0.1544704249198182</v>
       </c>
       <c r="T21">
-        <v>1.289441294181889</v>
+        <v>1.301843688837112</v>
       </c>
       <c r="U21">
         <v>0.0503</v>
@@ -3047,7 +3047,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>22.29537753237659</v>
+        <v>21.18060865575776</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3055,22 +3055,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1309201399358546</v>
+        <v>0.1305812029614076</v>
       </c>
       <c r="C22">
-        <v>32.60941367775391</v>
+        <v>32.35230887731696</v>
       </c>
       <c r="D22">
-        <v>40.40941367775391</v>
+        <v>40.54230887731696</v>
       </c>
       <c r="E22">
-        <v>-10</v>
+        <v>-9.609999999999999</v>
       </c>
       <c r="F22">
-        <v>7.800000000000001</v>
+        <v>8.190000000000001</v>
       </c>
       <c r="G22">
         <v>0</v>
@@ -3091,28 +3091,28 @@
         <v>8.31</v>
       </c>
       <c r="M22">
-        <v>0.39234</v>
+        <v>0.411957</v>
       </c>
       <c r="N22">
-        <v>7.917660000000001</v>
+        <v>7.898043</v>
       </c>
       <c r="O22">
-        <v>2.1377682</v>
+        <v>2.13247161</v>
       </c>
       <c r="P22">
-        <v>5.7798918</v>
+        <v>5.76557139</v>
       </c>
       <c r="Q22">
-        <v>6.6198918</v>
+        <v>6.60557139</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1544704249198182</v>
+        <v>0.1555319151410223</v>
       </c>
       <c r="T22">
-        <v>1.301843688837112</v>
+        <v>1.31456006816715</v>
       </c>
       <c r="U22">
         <v>0.0503</v>
@@ -3129,7 +3129,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>21.18060865575776</v>
+        <v>20.17200824357882</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3137,22 +3137,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1305812029614076</v>
+        <v>0.1302422659869606</v>
       </c>
       <c r="C23">
-        <v>32.35230887731696</v>
+        <v>32.09608107095668</v>
       </c>
       <c r="D23">
-        <v>40.54230887731696</v>
+        <v>40.67608107095668</v>
       </c>
       <c r="E23">
-        <v>-9.610000000000001</v>
+        <v>-9.220000000000001</v>
       </c>
       <c r="F23">
-        <v>8.19</v>
+        <v>8.58</v>
       </c>
       <c r="G23">
         <v>0</v>
@@ -3173,28 +3173,28 @@
         <v>8.31</v>
       </c>
       <c r="M23">
-        <v>0.411957</v>
+        <v>0.431574</v>
       </c>
       <c r="N23">
-        <v>7.898043</v>
+        <v>7.878426</v>
       </c>
       <c r="O23">
-        <v>2.13247161</v>
+        <v>2.12717502</v>
       </c>
       <c r="P23">
-        <v>5.76557139</v>
+        <v>5.75125098</v>
       </c>
       <c r="Q23">
-        <v>6.60557139</v>
+        <v>6.59125098</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1555319151410223</v>
+        <v>0.156620623060206</v>
       </c>
       <c r="T23">
-        <v>1.31456006816715</v>
+        <v>1.327602508505651</v>
       </c>
       <c r="U23">
         <v>0.0503</v>
@@ -3211,7 +3211,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>20.17200824357882</v>
+        <v>19.2550987779616</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3219,22 +3219,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1302422659869606</v>
+        <v>0.1299033290125137</v>
       </c>
       <c r="C24">
-        <v>32.09608107095668</v>
+        <v>31.84073896852232</v>
       </c>
       <c r="D24">
-        <v>40.67608107095668</v>
+        <v>40.81073896852232</v>
       </c>
       <c r="E24">
-        <v>-9.220000000000001</v>
+        <v>-8.83</v>
       </c>
       <c r="F24">
-        <v>8.58</v>
+        <v>8.970000000000001</v>
       </c>
       <c r="G24">
         <v>0</v>
@@ -3255,28 +3255,28 @@
         <v>8.31</v>
       </c>
       <c r="M24">
-        <v>0.431574</v>
+        <v>0.451191</v>
       </c>
       <c r="N24">
-        <v>7.878426</v>
+        <v>7.858809000000001</v>
       </c>
       <c r="O24">
-        <v>2.12717502</v>
+        <v>2.12187843</v>
       </c>
       <c r="P24">
-        <v>5.75125098</v>
+        <v>5.73693057</v>
       </c>
       <c r="Q24">
-        <v>6.59125098</v>
+        <v>6.57693057</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.156620623060206</v>
+        <v>0.1577376091071607</v>
       </c>
       <c r="T24">
-        <v>1.327602508505651</v>
+        <v>1.340983713528269</v>
       </c>
       <c r="U24">
         <v>0.0503</v>
@@ -3293,7 +3293,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>19.2550987779616</v>
+        <v>18.41792057022414</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3301,22 +3301,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1299033290125137</v>
+        <v>0.1295643920380668</v>
       </c>
       <c r="C25">
-        <v>31.84073896852232</v>
+        <v>31.58629139558188</v>
       </c>
       <c r="D25">
-        <v>40.81073896852232</v>
+        <v>40.94629139558188</v>
       </c>
       <c r="E25">
-        <v>-8.83</v>
+        <v>-8.44</v>
       </c>
       <c r="F25">
-        <v>8.970000000000001</v>
+        <v>9.360000000000001</v>
       </c>
       <c r="G25">
         <v>0</v>
@@ -3337,28 +3337,28 @@
         <v>8.31</v>
       </c>
       <c r="M25">
-        <v>0.451191</v>
+        <v>0.4708080000000001</v>
       </c>
       <c r="N25">
-        <v>7.858809000000001</v>
+        <v>7.839192000000001</v>
       </c>
       <c r="O25">
-        <v>2.12187843</v>
+        <v>2.11658184</v>
       </c>
       <c r="P25">
-        <v>5.73693057</v>
+        <v>5.72261016</v>
       </c>
       <c r="Q25">
-        <v>6.57693057</v>
+        <v>6.56261016</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1577376091071607</v>
+        <v>0.1588839895237721</v>
       </c>
       <c r="T25">
-        <v>1.340983713528269</v>
+        <v>1.354717055525166</v>
       </c>
       <c r="U25">
         <v>0.0503</v>
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>18.41792057022414</v>
+        <v>17.65050721313147</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3383,22 +3383,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1295643920380668</v>
+        <v>0.1292254550636198</v>
       </c>
       <c r="C26">
-        <v>31.58629139558188</v>
+        <v>31.3327472953502</v>
       </c>
       <c r="D26">
-        <v>40.94629139558188</v>
+        <v>41.0827472953502</v>
       </c>
       <c r="E26">
-        <v>-8.440000000000001</v>
+        <v>-8.050000000000001</v>
       </c>
       <c r="F26">
-        <v>9.359999999999999</v>
+        <v>9.75</v>
       </c>
       <c r="G26">
         <v>0</v>
@@ -3419,28 +3419,28 @@
         <v>8.31</v>
       </c>
       <c r="M26">
-        <v>0.4708079999999999</v>
+        <v>0.490425</v>
       </c>
       <c r="N26">
-        <v>7.839192000000001</v>
+        <v>7.819575</v>
       </c>
       <c r="O26">
-        <v>2.11658184</v>
+        <v>2.11128525</v>
       </c>
       <c r="P26">
-        <v>5.72261016</v>
+        <v>5.70828975</v>
       </c>
       <c r="Q26">
-        <v>6.56261016</v>
+        <v>6.54828975</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1588839895237721</v>
+        <v>0.1600609400848264</v>
       </c>
       <c r="T26">
-        <v>1.354717055525166</v>
+        <v>1.368816619975314</v>
       </c>
       <c r="U26">
         <v>0.0503</v>
@@ -3457,7 +3457,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>17.65050721313147</v>
+        <v>16.94448692460621</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3465,22 +3465,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1292254550636198</v>
+        <v>0.1288865180891729</v>
       </c>
       <c r="C27">
-        <v>31.3327472953502</v>
+        <v>31.08011573065584</v>
       </c>
       <c r="D27">
-        <v>41.0827472953502</v>
+        <v>41.22011573065584</v>
       </c>
       <c r="E27">
-        <v>-8.050000000000001</v>
+        <v>-7.66</v>
       </c>
       <c r="F27">
-        <v>9.75</v>
+        <v>10.14</v>
       </c>
       <c r="G27">
         <v>0</v>
@@ -3501,28 +3501,28 @@
         <v>8.31</v>
       </c>
       <c r="M27">
-        <v>0.490425</v>
+        <v>0.510042</v>
       </c>
       <c r="N27">
-        <v>7.819575</v>
+        <v>7.799958</v>
       </c>
       <c r="O27">
-        <v>2.11128525</v>
+        <v>2.10598866</v>
       </c>
       <c r="P27">
-        <v>5.70828975</v>
+        <v>5.69396934</v>
       </c>
       <c r="Q27">
-        <v>6.54828975</v>
+        <v>6.53396934</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1600609400848264</v>
+        <v>0.1612697001205039</v>
       </c>
       <c r="T27">
-        <v>1.368816619975314</v>
+        <v>1.383297253734925</v>
       </c>
       <c r="U27">
         <v>0.0503</v>
@@ -3539,7 +3539,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>16.94448692460621</v>
+        <v>16.29277588904443</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3547,22 +3547,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1288865180891729</v>
+        <v>0.1285475811147259</v>
       </c>
       <c r="C28">
-        <v>31.08011573065584</v>
+        <v>30.82840588594767</v>
       </c>
       <c r="D28">
-        <v>41.22011573065584</v>
+        <v>41.35840588594767</v>
       </c>
       <c r="E28">
-        <v>-7.66</v>
+        <v>-7.27</v>
       </c>
       <c r="F28">
-        <v>10.14</v>
+        <v>10.53</v>
       </c>
       <c r="G28">
         <v>0</v>
@@ -3583,28 +3583,28 @@
         <v>8.31</v>
       </c>
       <c r="M28">
-        <v>0.510042</v>
+        <v>0.529659</v>
       </c>
       <c r="N28">
-        <v>7.799958</v>
+        <v>7.780341000000001</v>
       </c>
       <c r="O28">
-        <v>2.10598866</v>
+        <v>2.10069207</v>
       </c>
       <c r="P28">
-        <v>5.69396934</v>
+        <v>5.679648930000001</v>
       </c>
       <c r="Q28">
-        <v>6.53396934</v>
+        <v>6.519648930000001</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1612697001205039</v>
+        <v>0.1625115768694876</v>
       </c>
       <c r="T28">
-        <v>1.383297253734925</v>
+        <v>1.398174617186581</v>
       </c>
       <c r="U28">
         <v>0.0503</v>
@@ -3621,7 +3621,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>16.29277588904443</v>
+        <v>15.68933974500575</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3629,22 +3629,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1285475811147259</v>
+        <v>0.128208644140279</v>
       </c>
       <c r="C29">
-        <v>30.82840588594767</v>
+        <v>30.57762706934171</v>
       </c>
       <c r="D29">
-        <v>41.35840588594767</v>
+        <v>41.49762706934171</v>
       </c>
       <c r="E29">
-        <v>-7.27</v>
+        <v>-6.879999999999999</v>
       </c>
       <c r="F29">
-        <v>10.53</v>
+        <v>10.92</v>
       </c>
       <c r="G29">
         <v>0</v>
@@ -3665,28 +3665,28 @@
         <v>8.31</v>
       </c>
       <c r="M29">
-        <v>0.529659</v>
+        <v>0.5492760000000001</v>
       </c>
       <c r="N29">
-        <v>7.780341000000001</v>
+        <v>7.760724000000001</v>
       </c>
       <c r="O29">
-        <v>2.10069207</v>
+        <v>2.09539548</v>
       </c>
       <c r="P29">
-        <v>5.679648930000001</v>
+        <v>5.665328520000001</v>
       </c>
       <c r="Q29">
-        <v>6.519648930000001</v>
+        <v>6.505328520000001</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1625115768694876</v>
+        <v>0.1637879501948319</v>
       </c>
       <c r="T29">
-        <v>1.398174617186581</v>
+        <v>1.413465240734115</v>
       </c>
       <c r="U29">
         <v>0.0503</v>
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>15.68933974500575</v>
+        <v>15.12900618268411</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3711,22 +3711,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.128208644140279</v>
+        <v>0.127869707165832</v>
       </c>
       <c r="C30">
-        <v>30.57762706934171</v>
+        <v>30.32778871470974</v>
       </c>
       <c r="D30">
-        <v>41.49762706934171</v>
+        <v>41.63778871470974</v>
       </c>
       <c r="E30">
-        <v>-6.879999999999999</v>
+        <v>-6.489999999999998</v>
       </c>
       <c r="F30">
-        <v>10.92</v>
+        <v>11.31</v>
       </c>
       <c r="G30">
         <v>0</v>
@@ -3747,28 +3747,28 @@
         <v>8.31</v>
       </c>
       <c r="M30">
-        <v>0.5492760000000001</v>
+        <v>0.5688930000000001</v>
       </c>
       <c r="N30">
-        <v>7.760724000000001</v>
+        <v>7.741107</v>
       </c>
       <c r="O30">
-        <v>2.09539548</v>
+        <v>2.09009889</v>
       </c>
       <c r="P30">
-        <v>5.665328520000001</v>
+        <v>5.65100811</v>
       </c>
       <c r="Q30">
-        <v>6.505328520000001</v>
+        <v>6.49100811</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1637879501948319</v>
+        <v>0.165100277698355</v>
       </c>
       <c r="T30">
-        <v>1.413465240734115</v>
+        <v>1.429186586071721</v>
       </c>
       <c r="U30">
         <v>0.0503</v>
@@ -3785,7 +3785,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>15.12900618268411</v>
+        <v>14.6073163143157</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3793,22 +3793,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.127869707165832</v>
+        <v>0.1275307701913851</v>
       </c>
       <c r="C31">
-        <v>30.32778871470974</v>
+        <v>30.07890038381016</v>
       </c>
       <c r="D31">
-        <v>41.63778871470974</v>
+        <v>41.77890038381016</v>
       </c>
       <c r="E31">
-        <v>-6.490000000000002</v>
+        <v>-6.100000000000001</v>
       </c>
       <c r="F31">
-        <v>11.31</v>
+        <v>11.7</v>
       </c>
       <c r="G31">
         <v>0</v>
@@ -3829,28 +3829,28 @@
         <v>8.31</v>
       </c>
       <c r="M31">
-        <v>0.5688929999999999</v>
+        <v>0.58851</v>
       </c>
       <c r="N31">
-        <v>7.741107</v>
+        <v>7.72149</v>
       </c>
       <c r="O31">
-        <v>2.09009889</v>
+        <v>2.0848023</v>
       </c>
       <c r="P31">
-        <v>5.65100811</v>
+        <v>5.6366877</v>
       </c>
       <c r="Q31">
-        <v>6.49100811</v>
+        <v>6.476687699999999</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.165100277698355</v>
+        <v>0.1664501002734073</v>
       </c>
       <c r="T31">
-        <v>1.429186586071721</v>
+        <v>1.445357112704688</v>
       </c>
       <c r="U31">
         <v>0.0503</v>
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>14.6073163143157</v>
+        <v>14.12040577050517</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1275307701913851</v>
+        <v>0.1271918332169382</v>
       </c>
       <c r="C32">
-        <v>30.07890038381016</v>
+        <v>29.83097176846248</v>
       </c>
       <c r="D32">
-        <v>41.77890038381016</v>
+        <v>41.92097176846248</v>
       </c>
       <c r="E32">
-        <v>-6.100000000000001</v>
+        <v>-5.710000000000001</v>
       </c>
       <c r="F32">
-        <v>11.7</v>
+        <v>12.09</v>
       </c>
       <c r="G32">
         <v>0</v>
@@ -3911,28 +3911,28 @@
         <v>8.31</v>
       </c>
       <c r="M32">
-        <v>0.58851</v>
+        <v>0.608127</v>
       </c>
       <c r="N32">
-        <v>7.72149</v>
+        <v>7.701873000000001</v>
       </c>
       <c r="O32">
-        <v>2.0848023</v>
+        <v>2.07950571</v>
       </c>
       <c r="P32">
-        <v>5.6366877</v>
+        <v>5.622367290000001</v>
       </c>
       <c r="Q32">
-        <v>6.476687699999999</v>
+        <v>6.46236729</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1664501002734073</v>
+        <v>0.1678390481404901</v>
       </c>
       <c r="T32">
-        <v>1.445357112704688</v>
+        <v>1.461996350254552</v>
       </c>
       <c r="U32">
         <v>0.0503</v>
@@ -3949,7 +3949,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>14.12040577050517</v>
+        <v>13.6649088101663</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3957,22 +3957,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1271918332169382</v>
+        <v>0.1268528962424912</v>
       </c>
       <c r="C33">
-        <v>29.83097176846248</v>
+        <v>29.58401269276621</v>
       </c>
       <c r="D33">
-        <v>41.92097176846248</v>
+        <v>42.06401269276621</v>
       </c>
       <c r="E33">
-        <v>-5.710000000000001</v>
+        <v>-5.32</v>
       </c>
       <c r="F33">
-        <v>12.09</v>
+        <v>12.48</v>
       </c>
       <c r="G33">
         <v>0</v>
@@ -3993,28 +3993,28 @@
         <v>8.31</v>
       </c>
       <c r="M33">
-        <v>0.608127</v>
+        <v>0.627744</v>
       </c>
       <c r="N33">
-        <v>7.701873000000001</v>
+        <v>7.682256000000001</v>
       </c>
       <c r="O33">
-        <v>2.07950571</v>
+        <v>2.07420912</v>
       </c>
       <c r="P33">
-        <v>5.622367290000001</v>
+        <v>5.60804688</v>
       </c>
       <c r="Q33">
-        <v>6.46236729</v>
+        <v>6.44804688</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1678390481404901</v>
+        <v>0.1692688474154283</v>
       </c>
       <c r="T33">
-        <v>1.461996350254552</v>
+        <v>1.479124977144118</v>
       </c>
       <c r="U33">
         <v>0.0503</v>
@@ -4031,7 +4031,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>13.6649088101663</v>
+        <v>13.2378804098486</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4039,22 +4039,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1268528962424912</v>
+        <v>0.1268753092680443</v>
       </c>
       <c r="C34">
-        <v>29.58401269276621</v>
+        <v>29.1845236321231</v>
       </c>
       <c r="D34">
-        <v>42.06401269276621</v>
+        <v>42.0545236321231</v>
       </c>
       <c r="E34">
-        <v>-5.32</v>
+        <v>-4.93</v>
       </c>
       <c r="F34">
-        <v>12.48</v>
+        <v>12.87</v>
       </c>
       <c r="G34">
         <v>0</v>
@@ -4075,45 +4075,45 @@
         <v>8.31</v>
       </c>
       <c r="M34">
-        <v>0.627744</v>
+        <v>0.6666660000000001</v>
       </c>
       <c r="N34">
-        <v>7.682256000000001</v>
+        <v>7.643334</v>
       </c>
       <c r="O34">
-        <v>2.07420912</v>
+        <v>2.06370018</v>
       </c>
       <c r="P34">
-        <v>5.60804688</v>
+        <v>5.57963382</v>
       </c>
       <c r="Q34">
-        <v>6.44804688</v>
+        <v>6.41963382</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1692688474154283</v>
+        <v>0.1707413272657377</v>
       </c>
       <c r="T34">
-        <v>1.479124977144118</v>
+        <v>1.496764906328894</v>
       </c>
       <c r="U34">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V34">
         <v>0.27</v>
       </c>
       <c r="W34">
-        <v>0.03671899999999999</v>
+        <v>0.037814</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y34">
-        <v>13.2378804098486</v>
+        <v>12.46501246501246</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4121,22 +4121,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1268753092680443</v>
+        <v>0.1265473222935973</v>
       </c>
       <c r="C35">
-        <v>29.1845236321231</v>
+        <v>28.933812819486</v>
       </c>
       <c r="D35">
-        <v>42.0545236321231</v>
+        <v>42.193812819486</v>
       </c>
       <c r="E35">
-        <v>-4.93</v>
+        <v>-4.539999999999999</v>
       </c>
       <c r="F35">
-        <v>12.87</v>
+        <v>13.26</v>
       </c>
       <c r="G35">
         <v>0</v>
@@ -4157,28 +4157,28 @@
         <v>8.31</v>
       </c>
       <c r="M35">
-        <v>0.6666660000000001</v>
+        <v>0.686868</v>
       </c>
       <c r="N35">
-        <v>7.643334</v>
+        <v>7.623132</v>
       </c>
       <c r="O35">
-        <v>2.06370018</v>
+        <v>2.05824564</v>
       </c>
       <c r="P35">
-        <v>5.57963382</v>
+        <v>5.56488636</v>
       </c>
       <c r="Q35">
-        <v>6.41963382</v>
+        <v>6.40488636</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1707413272657377</v>
+        <v>0.1722584277175717</v>
       </c>
       <c r="T35">
-        <v>1.496764906328894</v>
+        <v>1.514939378822301</v>
       </c>
       <c r="U35">
         <v>0.0518</v>
@@ -4195,7 +4195,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>12.46501246501246</v>
+        <v>12.09839445133563</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4203,22 +4203,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1265473222935973</v>
+        <v>0.1262193353191504</v>
       </c>
       <c r="C36">
-        <v>28.933812819486</v>
+        <v>28.68402775511074</v>
       </c>
       <c r="D36">
-        <v>42.193812819486</v>
+        <v>42.33402775511074</v>
       </c>
       <c r="E36">
-        <v>-4.539999999999999</v>
+        <v>-4.149999999999999</v>
       </c>
       <c r="F36">
-        <v>13.26</v>
+        <v>13.65</v>
       </c>
       <c r="G36">
         <v>0</v>
@@ -4239,28 +4239,28 @@
         <v>8.31</v>
       </c>
       <c r="M36">
-        <v>0.686868</v>
+        <v>0.7070700000000001</v>
       </c>
       <c r="N36">
-        <v>7.623132</v>
+        <v>7.602930000000001</v>
       </c>
       <c r="O36">
-        <v>2.05824564</v>
+        <v>2.0527911</v>
       </c>
       <c r="P36">
-        <v>5.56488636</v>
+        <v>5.5501389</v>
       </c>
       <c r="Q36">
-        <v>6.40488636</v>
+        <v>6.3901389</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1722584277175717</v>
+        <v>0.1738222081833083</v>
       </c>
       <c r="T36">
-        <v>1.514939378822301</v>
+        <v>1.533673065853966</v>
       </c>
       <c r="U36">
         <v>0.0518</v>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>12.09839445133563</v>
+        <v>11.75272603844032</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4285,22 +4285,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1262193353191504</v>
+        <v>0.1258913483447035</v>
       </c>
       <c r="C37">
-        <v>28.68402775511074</v>
+        <v>28.43517769887564</v>
       </c>
       <c r="D37">
-        <v>42.33402775511074</v>
+        <v>42.47517769887564</v>
       </c>
       <c r="E37">
-        <v>-4.149999999999999</v>
+        <v>-3.76</v>
       </c>
       <c r="F37">
-        <v>13.65</v>
+        <v>14.04</v>
       </c>
       <c r="G37">
         <v>0</v>
@@ -4321,28 +4321,28 @@
         <v>8.31</v>
       </c>
       <c r="M37">
-        <v>0.7070700000000001</v>
+        <v>0.727272</v>
       </c>
       <c r="N37">
-        <v>7.602930000000001</v>
+        <v>7.582728</v>
       </c>
       <c r="O37">
-        <v>2.0527911</v>
+        <v>2.04733656</v>
       </c>
       <c r="P37">
-        <v>5.5501389</v>
+        <v>5.53539144</v>
       </c>
       <c r="Q37">
-        <v>6.3901389</v>
+        <v>6.37539144</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1738222081833083</v>
+        <v>0.1754348567885992</v>
       </c>
       <c r="T37">
-        <v>1.533673065853966</v>
+        <v>1.55299218060537</v>
       </c>
       <c r="U37">
         <v>0.0518</v>
@@ -4359,7 +4359,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>11.75272603844032</v>
+        <v>11.42626142626143</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4367,22 +4367,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1258913483447035</v>
+        <v>0.1255633613702565</v>
       </c>
       <c r="C38">
-        <v>28.43517769887564</v>
+        <v>28.18727203456915</v>
       </c>
       <c r="D38">
-        <v>42.47517769887564</v>
+        <v>42.61727203456915</v>
       </c>
       <c r="E38">
-        <v>-3.760000000000002</v>
+        <v>-3.370000000000001</v>
       </c>
       <c r="F38">
-        <v>14.04</v>
+        <v>14.43</v>
       </c>
       <c r="G38">
         <v>0</v>
@@ -4403,28 +4403,28 @@
         <v>8.31</v>
       </c>
       <c r="M38">
-        <v>0.7272719999999999</v>
+        <v>0.747474</v>
       </c>
       <c r="N38">
-        <v>7.582728</v>
+        <v>7.562526</v>
       </c>
       <c r="O38">
-        <v>2.04733656</v>
+        <v>2.04188202</v>
       </c>
       <c r="P38">
-        <v>5.53539144</v>
+        <v>5.52064398</v>
       </c>
       <c r="Q38">
-        <v>6.37539144</v>
+        <v>6.36064398</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1754348567885992</v>
+        <v>0.1770987005877088</v>
       </c>
       <c r="T38">
-        <v>1.55299218060537</v>
+        <v>1.572924600586978</v>
       </c>
       <c r="U38">
         <v>0.0518</v>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>11.42626142626143</v>
+        <v>11.11744354987598</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4449,22 +4449,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1255633613702565</v>
+        <v>0.1252353743958096</v>
       </c>
       <c r="C39">
-        <v>28.18727203456915</v>
+        <v>27.94032027196943</v>
       </c>
       <c r="D39">
-        <v>42.61727203456915</v>
+        <v>42.76032027196943</v>
       </c>
       <c r="E39">
-        <v>-3.370000000000001</v>
+        <v>-2.98</v>
       </c>
       <c r="F39">
-        <v>14.43</v>
+        <v>14.82</v>
       </c>
       <c r="G39">
         <v>0</v>
@@ -4485,28 +4485,28 @@
         <v>8.31</v>
       </c>
       <c r="M39">
-        <v>0.747474</v>
+        <v>0.767676</v>
       </c>
       <c r="N39">
-        <v>7.562526</v>
+        <v>7.542324000000001</v>
       </c>
       <c r="O39">
-        <v>2.04188202</v>
+        <v>2.03642748</v>
       </c>
       <c r="P39">
-        <v>5.52064398</v>
+        <v>5.50589652</v>
       </c>
       <c r="Q39">
-        <v>6.36064398</v>
+        <v>6.34589652</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1770987005877088</v>
+        <v>0.1788162167674348</v>
       </c>
       <c r="T39">
-        <v>1.572924600586978</v>
+        <v>1.593500001858315</v>
       </c>
       <c r="U39">
         <v>0.0518</v>
@@ -4523,7 +4523,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>11.11744354987598</v>
+        <v>10.82487924593188</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4531,22 +4531,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1252353743958096</v>
+        <v>0.1249073874213626</v>
       </c>
       <c r="C40">
-        <v>27.94032027196943</v>
+        <v>27.6943320489659</v>
       </c>
       <c r="D40">
-        <v>42.76032027196943</v>
+        <v>42.90433204896591</v>
       </c>
       <c r="E40">
-        <v>-2.98</v>
+        <v>-2.59</v>
       </c>
       <c r="F40">
-        <v>14.82</v>
+        <v>15.21</v>
       </c>
       <c r="G40">
         <v>0</v>
@@ -4567,28 +4567,28 @@
         <v>8.31</v>
       </c>
       <c r="M40">
-        <v>0.767676</v>
+        <v>0.7878780000000001</v>
       </c>
       <c r="N40">
-        <v>7.542324000000001</v>
+        <v>7.522122</v>
       </c>
       <c r="O40">
-        <v>2.03642748</v>
+        <v>2.03097294</v>
       </c>
       <c r="P40">
-        <v>5.50589652</v>
+        <v>5.49114906</v>
       </c>
       <c r="Q40">
-        <v>6.34589652</v>
+        <v>6.33114906</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1788162167674348</v>
+        <v>0.1805900449530535</v>
       </c>
       <c r="T40">
-        <v>1.593500001858315</v>
+        <v>1.614750006450024</v>
       </c>
       <c r="U40">
         <v>0.0518</v>
@@ -4605,7 +4605,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>10.82487924593188</v>
+        <v>10.54731823962593</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4613,22 +4613,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1249073874213626</v>
+        <v>0.1245794004469157</v>
       </c>
       <c r="C41">
-        <v>27.6943320489659</v>
+        <v>27.44931713372394</v>
       </c>
       <c r="D41">
-        <v>42.90433204896591</v>
+        <v>43.04931713372394</v>
       </c>
       <c r="E41">
-        <v>-2.59</v>
+        <v>-2.199999999999999</v>
       </c>
       <c r="F41">
-        <v>15.21</v>
+        <v>15.6</v>
       </c>
       <c r="G41">
         <v>0</v>
@@ -4649,28 +4649,28 @@
         <v>8.31</v>
       </c>
       <c r="M41">
-        <v>0.7878780000000001</v>
+        <v>0.80808</v>
       </c>
       <c r="N41">
-        <v>7.522122</v>
+        <v>7.50192</v>
       </c>
       <c r="O41">
-        <v>2.03097294</v>
+        <v>2.0255184</v>
       </c>
       <c r="P41">
-        <v>5.49114906</v>
+        <v>5.4764016</v>
       </c>
       <c r="Q41">
-        <v>6.33114906</v>
+        <v>6.3164016</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1805900449530535</v>
+        <v>0.1824230007448595</v>
       </c>
       <c r="T41">
-        <v>1.614750006450024</v>
+        <v>1.636708344528123</v>
       </c>
       <c r="U41">
         <v>0.0518</v>
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>10.54731823962593</v>
+        <v>10.28363528363528</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4695,22 +4695,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1245794004469157</v>
+        <v>0.1242514134724687</v>
       </c>
       <c r="C42">
-        <v>27.44931713372394</v>
+        <v>27.20528542689347</v>
       </c>
       <c r="D42">
-        <v>43.04931713372394</v>
+        <v>43.19528542689347</v>
       </c>
       <c r="E42">
-        <v>-2.199999999999999</v>
+        <v>-1.809999999999999</v>
       </c>
       <c r="F42">
-        <v>15.6</v>
+        <v>15.99</v>
       </c>
       <c r="G42">
         <v>0</v>
@@ -4731,28 +4731,28 @@
         <v>8.31</v>
       </c>
       <c r="M42">
-        <v>0.80808</v>
+        <v>0.8282820000000001</v>
       </c>
       <c r="N42">
-        <v>7.50192</v>
+        <v>7.481718000000001</v>
       </c>
       <c r="O42">
-        <v>2.0255184</v>
+        <v>2.02006386</v>
       </c>
       <c r="P42">
-        <v>5.4764016</v>
+        <v>5.46165414</v>
       </c>
       <c r="Q42">
-        <v>6.3164016</v>
+        <v>6.30165414</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1824230007448595</v>
+        <v>0.184318090631303</v>
       </c>
       <c r="T42">
-        <v>1.636708344528123</v>
+        <v>1.659411033049548</v>
       </c>
       <c r="U42">
         <v>0.0518</v>
@@ -4769,7 +4769,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>10.28363528363528</v>
+        <v>10.03281491086369</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4777,22 +4777,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1242514134724687</v>
+        <v>0.1244446464980218</v>
       </c>
       <c r="C43">
-        <v>27.20528542689347</v>
+        <v>26.72916886753001</v>
       </c>
       <c r="D43">
-        <v>43.19528542689347</v>
+        <v>43.10916886753002</v>
       </c>
       <c r="E43">
-        <v>-1.809999999999999</v>
+        <v>-1.419999999999998</v>
       </c>
       <c r="F43">
-        <v>15.99</v>
+        <v>16.38</v>
       </c>
       <c r="G43">
         <v>0</v>
@@ -4813,45 +4813,45 @@
         <v>8.31</v>
       </c>
       <c r="M43">
-        <v>0.8282820000000001</v>
+        <v>0.8763300000000002</v>
       </c>
       <c r="N43">
-        <v>7.481718000000001</v>
+        <v>7.43367</v>
       </c>
       <c r="O43">
-        <v>2.02006386</v>
+        <v>2.0070909</v>
       </c>
       <c r="P43">
-        <v>5.46165414</v>
+        <v>5.4265791</v>
       </c>
       <c r="Q43">
-        <v>6.30165414</v>
+        <v>6.2665791</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.184318090631303</v>
+        <v>0.1862785284448652</v>
       </c>
       <c r="T43">
-        <v>1.659411033049548</v>
+        <v>1.682896572899298</v>
       </c>
       <c r="U43">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V43">
         <v>0.27</v>
       </c>
       <c r="W43">
-        <v>0.037814</v>
+        <v>0.039055</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y43">
-        <v>10.03281491086369</v>
+        <v>9.482729108897331</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4859,22 +4859,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1244446464980218</v>
+        <v>0.1241290695235749</v>
       </c>
       <c r="C44">
-        <v>26.72916886753002</v>
+        <v>26.47998754553294</v>
       </c>
       <c r="D44">
-        <v>43.10916886753002</v>
+        <v>43.24998754553294</v>
       </c>
       <c r="E44">
-        <v>-1.420000000000002</v>
+        <v>-1.030000000000001</v>
       </c>
       <c r="F44">
-        <v>16.38</v>
+        <v>16.77</v>
       </c>
       <c r="G44">
         <v>0</v>
@@ -4895,28 +4895,28 @@
         <v>8.31</v>
       </c>
       <c r="M44">
-        <v>0.8763299999999999</v>
+        <v>0.897195</v>
       </c>
       <c r="N44">
-        <v>7.43367</v>
+        <v>7.412805000000001</v>
       </c>
       <c r="O44">
-        <v>2.0070909</v>
+        <v>2.00145735</v>
       </c>
       <c r="P44">
-        <v>5.4265791</v>
+        <v>5.41134765</v>
       </c>
       <c r="Q44">
-        <v>6.2665791</v>
+        <v>6.25134765</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1862785284448652</v>
+        <v>0.1883077535501314</v>
       </c>
       <c r="T44">
-        <v>1.682896572899297</v>
+        <v>1.707206166778862</v>
       </c>
       <c r="U44">
         <v>0.0535</v>
@@ -4933,7 +4933,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>9.482729108897335</v>
+        <v>9.262200524969488</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1241290695235749</v>
+        <v>0.1238134925491279</v>
       </c>
       <c r="C45">
-        <v>26.47998754553294</v>
+        <v>26.23172922383666</v>
       </c>
       <c r="D45">
-        <v>43.24998754553294</v>
+        <v>43.39172922383666</v>
       </c>
       <c r="E45">
-        <v>-1.030000000000001</v>
+        <v>-0.6400000000000006</v>
       </c>
       <c r="F45">
-        <v>16.77</v>
+        <v>17.16</v>
       </c>
       <c r="G45">
         <v>0</v>
@@ -4977,28 +4977,28 @@
         <v>8.31</v>
       </c>
       <c r="M45">
-        <v>0.897195</v>
+        <v>0.91806</v>
       </c>
       <c r="N45">
-        <v>7.412805000000001</v>
+        <v>7.391940000000001</v>
       </c>
       <c r="O45">
-        <v>2.00145735</v>
+        <v>1.9958238</v>
       </c>
       <c r="P45">
-        <v>5.41134765</v>
+        <v>5.396116200000001</v>
       </c>
       <c r="Q45">
-        <v>6.25134765</v>
+        <v>6.236116200000001</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1883077535501314</v>
+        <v>0.1904094509805856</v>
       </c>
       <c r="T45">
-        <v>1.707206166778862</v>
+        <v>1.732383960439841</v>
       </c>
       <c r="U45">
         <v>0.0535</v>
@@ -5015,7 +5015,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>9.262200524969488</v>
+        <v>9.05169596758382</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5023,22 +5023,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1238134925491279</v>
+        <v>0.123497915574681</v>
       </c>
       <c r="C46">
-        <v>26.23172922383666</v>
+        <v>25.98440300702954</v>
       </c>
       <c r="D46">
-        <v>43.39172922383666</v>
+        <v>43.53440300702954</v>
       </c>
       <c r="E46">
-        <v>-0.6400000000000006</v>
+        <v>-0.25</v>
       </c>
       <c r="F46">
-        <v>17.16</v>
+        <v>17.55</v>
       </c>
       <c r="G46">
         <v>0</v>
@@ -5059,28 +5059,28 @@
         <v>8.31</v>
       </c>
       <c r="M46">
-        <v>0.91806</v>
+        <v>0.938925</v>
       </c>
       <c r="N46">
-        <v>7.391940000000001</v>
+        <v>7.371075</v>
       </c>
       <c r="O46">
-        <v>1.9958238</v>
+        <v>1.99019025</v>
       </c>
       <c r="P46">
-        <v>5.396116200000001</v>
+        <v>5.38088475</v>
       </c>
       <c r="Q46">
-        <v>6.236116200000001</v>
+        <v>6.22088475</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1904094509805856</v>
+        <v>0.1925875737721472</v>
       </c>
       <c r="T46">
-        <v>1.732383960439841</v>
+        <v>1.758477310233945</v>
       </c>
       <c r="U46">
         <v>0.0535</v>
@@ -5097,7 +5097,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>9.05169596758382</v>
+        <v>8.850547168304178</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5105,22 +5105,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.123497915574681</v>
+        <v>0.1231823386002341</v>
       </c>
       <c r="C47">
-        <v>25.98440300702954</v>
+        <v>25.73801811984006</v>
       </c>
       <c r="D47">
-        <v>43.53440300702954</v>
+        <v>43.67801811984006</v>
       </c>
       <c r="E47">
-        <v>-0.25</v>
+        <v>0.1400000000000006</v>
       </c>
       <c r="F47">
-        <v>17.55</v>
+        <v>17.94</v>
       </c>
       <c r="G47">
         <v>0</v>
@@ -5141,28 +5141,28 @@
         <v>8.31</v>
       </c>
       <c r="M47">
-        <v>0.938925</v>
+        <v>0.95979</v>
       </c>
       <c r="N47">
-        <v>7.371075</v>
+        <v>7.350210000000001</v>
       </c>
       <c r="O47">
-        <v>1.99019025</v>
+        <v>1.9845567</v>
       </c>
       <c r="P47">
-        <v>5.38088475</v>
+        <v>5.3656533</v>
       </c>
       <c r="Q47">
-        <v>6.22088475</v>
+        <v>6.2056533</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1925875737721472</v>
+        <v>0.1948463677782112</v>
       </c>
       <c r="T47">
-        <v>1.758477310233945</v>
+        <v>1.785537080390795</v>
       </c>
       <c r="U47">
         <v>0.0535</v>
@@ -5179,7 +5179,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>8.850547168304178</v>
+        <v>8.658143968993219</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5187,22 +5187,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1231823386002341</v>
+        <v>0.1228667616257871</v>
       </c>
       <c r="C48">
-        <v>25.73801811984006</v>
+        <v>25.49258390912495</v>
       </c>
       <c r="D48">
-        <v>43.67801811984006</v>
+        <v>43.82258390912495</v>
       </c>
       <c r="E48">
-        <v>0.1400000000000006</v>
+        <v>0.5300000000000011</v>
       </c>
       <c r="F48">
-        <v>17.94</v>
+        <v>18.33</v>
       </c>
       <c r="G48">
         <v>0</v>
@@ -5223,28 +5223,28 @@
         <v>8.31</v>
       </c>
       <c r="M48">
-        <v>0.95979</v>
+        <v>0.9806550000000001</v>
       </c>
       <c r="N48">
-        <v>7.350210000000001</v>
+        <v>7.329345</v>
       </c>
       <c r="O48">
-        <v>1.9845567</v>
+        <v>1.97892315</v>
       </c>
       <c r="P48">
-        <v>5.3656533</v>
+        <v>5.35042185</v>
       </c>
       <c r="Q48">
-        <v>6.2056533</v>
+        <v>6.19042185</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1948463677782112</v>
+        <v>0.1971903992939379</v>
       </c>
       <c r="T48">
-        <v>1.785537080390795</v>
+        <v>1.81361797394979</v>
       </c>
       <c r="U48">
         <v>0.0535</v>
@@ -5261,7 +5261,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>8.658143968993219</v>
+        <v>8.473928139865702</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5269,22 +5269,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1228667616257871</v>
+        <v>0.1225511846513402</v>
       </c>
       <c r="C49">
-        <v>25.49258390912495</v>
+        <v>25.24810984589702</v>
       </c>
       <c r="D49">
-        <v>43.82258390912495</v>
+        <v>43.96810984589703</v>
       </c>
       <c r="E49">
-        <v>0.5300000000000011</v>
+        <v>0.9200000000000017</v>
       </c>
       <c r="F49">
-        <v>18.33</v>
+        <v>18.72</v>
       </c>
       <c r="G49">
         <v>0</v>
@@ -5305,28 +5305,28 @@
         <v>8.31</v>
       </c>
       <c r="M49">
-        <v>0.9806550000000001</v>
+        <v>1.00152</v>
       </c>
       <c r="N49">
-        <v>7.329345</v>
+        <v>7.30848</v>
       </c>
       <c r="O49">
-        <v>1.97892315</v>
+        <v>1.9732896</v>
       </c>
       <c r="P49">
-        <v>5.35042185</v>
+        <v>5.3351904</v>
       </c>
       <c r="Q49">
-        <v>6.19042185</v>
+        <v>6.1751904</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1971903992939379</v>
+        <v>0.1996245858679618</v>
       </c>
       <c r="T49">
-        <v>1.81361797394979</v>
+        <v>1.842778901876438</v>
       </c>
       <c r="U49">
         <v>0.0535</v>
@@ -5343,7 +5343,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>8.473928139865702</v>
+        <v>8.297387970285165</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5351,22 +5351,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1225511846513402</v>
+        <v>0.1222356076768932</v>
       </c>
       <c r="C50">
-        <v>25.24810984589703</v>
+        <v>25.00460552739351</v>
       </c>
       <c r="D50">
-        <v>43.96810984589703</v>
+        <v>44.11460552739351</v>
       </c>
       <c r="E50">
-        <v>0.9199999999999982</v>
+        <v>1.309999999999999</v>
       </c>
       <c r="F50">
-        <v>18.72</v>
+        <v>19.11</v>
       </c>
       <c r="G50">
         <v>0</v>
@@ -5387,28 +5387,28 @@
         <v>8.31</v>
       </c>
       <c r="M50">
-        <v>1.00152</v>
+        <v>1.022385</v>
       </c>
       <c r="N50">
-        <v>7.30848</v>
+        <v>7.287615000000001</v>
       </c>
       <c r="O50">
-        <v>1.9732896</v>
+        <v>1.96765605</v>
       </c>
       <c r="P50">
-        <v>5.3351904</v>
+        <v>5.31995895</v>
       </c>
       <c r="Q50">
-        <v>6.1751904</v>
+        <v>6.15995895</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1996245858679618</v>
+        <v>0.2021542307390063</v>
       </c>
       <c r="T50">
-        <v>1.842778901876438</v>
+        <v>1.873083395604131</v>
       </c>
       <c r="U50">
         <v>0.0535</v>
@@ -5425,7 +5425,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>8.297387970285168</v>
+        <v>8.128053521912001</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5433,22 +5433,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1222356076768932</v>
+        <v>0.1219200307024463</v>
       </c>
       <c r="C51">
-        <v>25.00460552739351</v>
+        <v>24.76208067918591</v>
       </c>
       <c r="D51">
-        <v>44.11460552739351</v>
+        <v>44.26208067918591</v>
       </c>
       <c r="E51">
-        <v>1.309999999999999</v>
+        <v>1.699999999999999</v>
       </c>
       <c r="F51">
-        <v>19.11</v>
+        <v>19.5</v>
       </c>
       <c r="G51">
         <v>0</v>
@@ -5469,28 +5469,28 @@
         <v>8.31</v>
       </c>
       <c r="M51">
-        <v>1.022385</v>
+        <v>1.04325</v>
       </c>
       <c r="N51">
-        <v>7.287615000000001</v>
+        <v>7.26675</v>
       </c>
       <c r="O51">
-        <v>1.96765605</v>
+        <v>1.9620225</v>
       </c>
       <c r="P51">
-        <v>5.31995895</v>
+        <v>5.3047275</v>
       </c>
       <c r="Q51">
-        <v>6.15995895</v>
+        <v>6.1447275</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.2021542307390063</v>
+        <v>0.2047850614048926</v>
       </c>
       <c r="T51">
-        <v>1.873083395604131</v>
+        <v>1.904600069080933</v>
       </c>
       <c r="U51">
         <v>0.0535</v>
@@ -5507,7 +5507,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>8.128053521912001</v>
+        <v>7.96549245147376</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5515,22 +5515,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1219200307024463</v>
+        <v>0.1216044537279994</v>
       </c>
       <c r="C52">
-        <v>24.76208067918591</v>
+        <v>24.52054515733237</v>
       </c>
       <c r="D52">
-        <v>44.26208067918591</v>
+        <v>44.41054515733237</v>
       </c>
       <c r="E52">
-        <v>1.699999999999999</v>
+        <v>2.09</v>
       </c>
       <c r="F52">
-        <v>19.5</v>
+        <v>19.89</v>
       </c>
       <c r="G52">
         <v>0</v>
@@ -5551,28 +5551,28 @@
         <v>8.31</v>
       </c>
       <c r="M52">
-        <v>1.04325</v>
+        <v>1.064115</v>
       </c>
       <c r="N52">
-        <v>7.26675</v>
+        <v>7.245885</v>
       </c>
       <c r="O52">
-        <v>1.9620225</v>
+        <v>1.95638895</v>
       </c>
       <c r="P52">
-        <v>5.3047275</v>
+        <v>5.28949605</v>
       </c>
       <c r="Q52">
-        <v>6.1447275</v>
+        <v>6.12949605</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.2047850614048926</v>
+        <v>0.2075232729142844</v>
       </c>
       <c r="T52">
-        <v>1.904600069080933</v>
+        <v>1.937403137393522</v>
       </c>
       <c r="U52">
         <v>0.0535</v>
@@ -5589,7 +5589,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>7.96549245147376</v>
+        <v>7.809306324974275</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5597,22 +5597,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1216044537279994</v>
+        <v>0.1212888767535524</v>
       </c>
       <c r="C53">
-        <v>24.52054515733237</v>
+        <v>24.28000895057335</v>
       </c>
       <c r="D53">
-        <v>44.41054515733237</v>
+        <v>44.56000895057335</v>
       </c>
       <c r="E53">
-        <v>2.09</v>
+        <v>2.48</v>
       </c>
       <c r="F53">
-        <v>19.89</v>
+        <v>20.28</v>
       </c>
       <c r="G53">
         <v>0</v>
@@ -5633,28 +5633,28 @@
         <v>8.31</v>
       </c>
       <c r="M53">
-        <v>1.064115</v>
+        <v>1.08498</v>
       </c>
       <c r="N53">
-        <v>7.245885</v>
+        <v>7.225020000000001</v>
       </c>
       <c r="O53">
-        <v>1.95638895</v>
+        <v>1.9507554</v>
       </c>
       <c r="P53">
-        <v>5.28949605</v>
+        <v>5.2742646</v>
       </c>
       <c r="Q53">
-        <v>6.12949605</v>
+        <v>6.1142646</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.2075232729142844</v>
+        <v>0.2103755765699008</v>
       </c>
       <c r="T53">
-        <v>1.937403137393522</v>
+        <v>1.971573000219135</v>
       </c>
       <c r="U53">
         <v>0.0535</v>
@@ -5671,7 +5671,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>7.809306324974275</v>
+        <v>7.659127357186308</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5679,22 +5679,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1212888767535524</v>
+        <v>0.1212828197791055</v>
       </c>
       <c r="C54">
-        <v>24.28000895057335</v>
+        <v>23.89288749974611</v>
       </c>
       <c r="D54">
-        <v>44.56000895057335</v>
+        <v>44.56288749974611</v>
       </c>
       <c r="E54">
-        <v>2.48</v>
+        <v>2.870000000000001</v>
       </c>
       <c r="F54">
-        <v>20.28</v>
+        <v>20.67</v>
       </c>
       <c r="G54">
         <v>0</v>
@@ -5715,45 +5715,45 @@
         <v>8.31</v>
       </c>
       <c r="M54">
-        <v>1.08498</v>
+        <v>1.122381</v>
       </c>
       <c r="N54">
-        <v>7.225020000000001</v>
+        <v>7.187619000000001</v>
       </c>
       <c r="O54">
-        <v>1.9507554</v>
+        <v>1.94065713</v>
       </c>
       <c r="P54">
-        <v>5.2742646</v>
+        <v>5.24696187</v>
       </c>
       <c r="Q54">
-        <v>6.1142646</v>
+        <v>6.08696187</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.2103755765699008</v>
+        <v>0.2133492548491606</v>
       </c>
       <c r="T54">
-        <v>1.971573000219135</v>
+        <v>2.007196899760732</v>
       </c>
       <c r="U54">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V54">
         <v>0.27</v>
       </c>
       <c r="W54">
-        <v>0.039055</v>
+        <v>0.039639</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y54">
-        <v>7.659127357186308</v>
+        <v>7.403902952740647</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5761,22 +5761,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1212828197791055</v>
+        <v>0.1209730828046585</v>
       </c>
       <c r="C55">
-        <v>23.89288749974611</v>
+        <v>23.65058598980693</v>
       </c>
       <c r="D55">
-        <v>44.56288749974611</v>
+        <v>44.71058598980694</v>
       </c>
       <c r="E55">
-        <v>2.870000000000001</v>
+        <v>3.260000000000002</v>
       </c>
       <c r="F55">
-        <v>20.67</v>
+        <v>21.06</v>
       </c>
       <c r="G55">
         <v>0</v>
@@ -5797,28 +5797,28 @@
         <v>8.31</v>
       </c>
       <c r="M55">
-        <v>1.122381</v>
+        <v>1.143558</v>
       </c>
       <c r="N55">
-        <v>7.187619000000001</v>
+        <v>7.166442</v>
       </c>
       <c r="O55">
-        <v>1.94065713</v>
+        <v>1.93493934</v>
       </c>
       <c r="P55">
-        <v>5.24696187</v>
+        <v>5.23150266</v>
       </c>
       <c r="Q55">
-        <v>6.08696187</v>
+        <v>6.07150266</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.2133492548491606</v>
+        <v>0.2164522234883881</v>
       </c>
       <c r="T55">
-        <v>2.007196899760732</v>
+        <v>2.04436966449979</v>
       </c>
       <c r="U55">
         <v>0.0543</v>
@@ -5835,7 +5835,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>7.403902952740647</v>
+        <v>7.266793638801005</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5843,22 +5843,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1209730828046585</v>
+        <v>0.1206633458302116</v>
       </c>
       <c r="C56">
-        <v>23.65058598980693</v>
+        <v>23.40926679445214</v>
       </c>
       <c r="D56">
-        <v>44.71058598980694</v>
+        <v>44.85926679445214</v>
       </c>
       <c r="E56">
-        <v>3.260000000000002</v>
+        <v>3.650000000000002</v>
       </c>
       <c r="F56">
-        <v>21.06</v>
+        <v>21.45</v>
       </c>
       <c r="G56">
         <v>0</v>
@@ -5879,28 +5879,28 @@
         <v>8.31</v>
       </c>
       <c r="M56">
-        <v>1.143558</v>
+        <v>1.164735</v>
       </c>
       <c r="N56">
-        <v>7.166442</v>
+        <v>7.145265</v>
       </c>
       <c r="O56">
-        <v>1.93493934</v>
+        <v>1.92922155</v>
       </c>
       <c r="P56">
-        <v>5.23150266</v>
+        <v>5.21604345</v>
       </c>
       <c r="Q56">
-        <v>6.07150266</v>
+        <v>6.05604345</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.2164522234883881</v>
+        <v>0.2196931018449146</v>
       </c>
       <c r="T56">
-        <v>2.04436966449979</v>
+        <v>2.083194552116139</v>
       </c>
       <c r="U56">
         <v>0.0543</v>
@@ -5917,7 +5917,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>7.266793638801005</v>
+        <v>7.134670118095532</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5925,22 +5925,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1206633458302116</v>
+        <v>0.1203536088557646</v>
       </c>
       <c r="C57">
-        <v>23.40926679445214</v>
+        <v>23.16893974616009</v>
       </c>
       <c r="D57">
-        <v>44.85926679445214</v>
+        <v>45.0089397461601</v>
       </c>
       <c r="E57">
-        <v>3.650000000000002</v>
+        <v>4.040000000000003</v>
       </c>
       <c r="F57">
-        <v>21.45</v>
+        <v>21.84</v>
       </c>
       <c r="G57">
         <v>0</v>
@@ -5961,28 +5961,28 @@
         <v>8.31</v>
       </c>
       <c r="M57">
-        <v>1.164735</v>
+        <v>1.185912</v>
       </c>
       <c r="N57">
-        <v>7.145265</v>
+        <v>7.124088</v>
       </c>
       <c r="O57">
-        <v>1.92922155</v>
+        <v>1.92350376</v>
       </c>
       <c r="P57">
-        <v>5.21604345</v>
+        <v>5.20058424</v>
       </c>
       <c r="Q57">
-        <v>6.05604345</v>
+        <v>6.04058424</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.2196931018449146</v>
+        <v>0.2230812928540105</v>
       </c>
       <c r="T57">
-        <v>2.083194552116139</v>
+        <v>2.123784207351413</v>
       </c>
       <c r="U57">
         <v>0.0543</v>
@@ -5999,7 +5999,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>7.134670118095532</v>
+        <v>7.007265294558111</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1203536088557646</v>
+        <v>0.1200438718813177</v>
       </c>
       <c r="C58">
-        <v>23.16893974616009</v>
+        <v>22.9296148090727</v>
       </c>
       <c r="D58">
-        <v>45.0089397461601</v>
+        <v>45.15961480907271</v>
       </c>
       <c r="E58">
-        <v>4.040000000000003</v>
+        <v>4.430000000000003</v>
       </c>
       <c r="F58">
-        <v>21.84</v>
+        <v>22.23</v>
       </c>
       <c r="G58">
         <v>0</v>
@@ -6043,28 +6043,28 @@
         <v>8.31</v>
       </c>
       <c r="M58">
-        <v>1.185912</v>
+        <v>1.207089</v>
       </c>
       <c r="N58">
-        <v>7.124088</v>
+        <v>7.102911000000001</v>
       </c>
       <c r="O58">
-        <v>1.92350376</v>
+        <v>1.91778597</v>
       </c>
       <c r="P58">
-        <v>5.20058424</v>
+        <v>5.18512503</v>
       </c>
       <c r="Q58">
-        <v>6.04058424</v>
+        <v>6.02512503</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.2230812928540105</v>
+        <v>0.2266270741425993</v>
       </c>
       <c r="T58">
-        <v>2.123784207351413</v>
+        <v>2.166261753527863</v>
       </c>
       <c r="U58">
         <v>0.0543</v>
@@ -6081,7 +6081,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>7.007265294558111</v>
+        <v>6.884330815706215</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6089,22 +6089,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1200438718813177</v>
+        <v>0.1197341349068708</v>
       </c>
       <c r="C59">
-        <v>22.9296148090727</v>
+        <v>22.69130208120669</v>
       </c>
       <c r="D59">
-        <v>45.15961480907271</v>
+        <v>45.3113020812067</v>
       </c>
       <c r="E59">
-        <v>4.430000000000003</v>
+        <v>4.820000000000004</v>
       </c>
       <c r="F59">
-        <v>22.23</v>
+        <v>22.62</v>
       </c>
       <c r="G59">
         <v>0</v>
@@ -6125,28 +6125,28 @@
         <v>8.31</v>
       </c>
       <c r="M59">
-        <v>1.207089</v>
+        <v>1.228266</v>
       </c>
       <c r="N59">
-        <v>7.102911000000001</v>
+        <v>7.081734</v>
       </c>
       <c r="O59">
-        <v>1.91778597</v>
+        <v>1.91206818</v>
       </c>
       <c r="P59">
-        <v>5.18512503</v>
+        <v>5.16966582</v>
       </c>
       <c r="Q59">
-        <v>6.02512503</v>
+        <v>6.009665819999999</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.2266270741425993</v>
+        <v>0.2303417021592161</v>
       </c>
       <c r="T59">
-        <v>2.166261753527863</v>
+        <v>2.21076203999843</v>
       </c>
       <c r="U59">
         <v>0.0543</v>
@@ -6163,7 +6163,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>6.884330815706215</v>
+        <v>6.765635456814728</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6171,22 +6171,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1197341349068707</v>
+        <v>0.1194243979324238</v>
       </c>
       <c r="C60">
-        <v>22.69130208120671</v>
+        <v>22.45401179670954</v>
       </c>
       <c r="D60">
-        <v>45.31130208120671</v>
+        <v>45.46401179670954</v>
       </c>
       <c r="E60">
-        <v>4.819999999999997</v>
+        <v>5.209999999999997</v>
       </c>
       <c r="F60">
-        <v>22.62</v>
+        <v>23.01</v>
       </c>
       <c r="G60">
         <v>0</v>
@@ -6207,28 +6207,28 @@
         <v>8.31</v>
       </c>
       <c r="M60">
-        <v>1.228266</v>
+        <v>1.249443</v>
       </c>
       <c r="N60">
-        <v>7.081734000000001</v>
+        <v>7.060557000000001</v>
       </c>
       <c r="O60">
-        <v>1.91206818</v>
+        <v>1.906350390000001</v>
       </c>
       <c r="P60">
-        <v>5.169665820000001</v>
+        <v>5.154206610000001</v>
       </c>
       <c r="Q60">
-        <v>6.00966582</v>
+        <v>5.994206610000001</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.230341702159216</v>
+        <v>0.234237531542497</v>
       </c>
       <c r="T60">
-        <v>2.210762039998428</v>
+        <v>2.257433072150486</v>
       </c>
       <c r="U60">
         <v>0.0543</v>
@@ -6245,7 +6245,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>6.765635456814731</v>
+        <v>6.650963669411091</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6253,22 +6253,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1194243979324238</v>
+        <v>0.1191146609579768</v>
       </c>
       <c r="C61">
-        <v>22.45401179670954</v>
+        <v>22.21775432816111</v>
       </c>
       <c r="D61">
-        <v>45.46401179670954</v>
+        <v>45.61775432816111</v>
       </c>
       <c r="E61">
-        <v>5.209999999999997</v>
+        <v>5.599999999999998</v>
       </c>
       <c r="F61">
-        <v>23.01</v>
+        <v>23.4</v>
       </c>
       <c r="G61">
         <v>0</v>
@@ -6289,28 +6289,28 @@
         <v>8.31</v>
       </c>
       <c r="M61">
-        <v>1.249443</v>
+        <v>1.27062</v>
       </c>
       <c r="N61">
-        <v>7.060557000000001</v>
+        <v>7.03938</v>
       </c>
       <c r="O61">
-        <v>1.906350390000001</v>
+        <v>1.9006326</v>
       </c>
       <c r="P61">
-        <v>5.154206610000001</v>
+        <v>5.1387474</v>
       </c>
       <c r="Q61">
-        <v>5.994206610000001</v>
+        <v>5.9787474</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.234237531542497</v>
+        <v>0.2383281523949421</v>
       </c>
       <c r="T61">
-        <v>2.257433072150486</v>
+        <v>2.306437655910146</v>
       </c>
       <c r="U61">
         <v>0.0543</v>
@@ -6327,7 +6327,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>6.650963669411091</v>
+        <v>6.540114274920906</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6335,22 +6335,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1191146609579768</v>
+        <v>0.1188049239835299</v>
       </c>
       <c r="C62">
-        <v>22.21775432816111</v>
+        <v>21.98254018892235</v>
       </c>
       <c r="D62">
-        <v>45.61775432816111</v>
+        <v>45.77254018892235</v>
       </c>
       <c r="E62">
-        <v>5.599999999999998</v>
+        <v>5.989999999999998</v>
       </c>
       <c r="F62">
-        <v>23.4</v>
+        <v>23.79</v>
       </c>
       <c r="G62">
         <v>0</v>
@@ -6371,28 +6371,28 @@
         <v>8.31</v>
       </c>
       <c r="M62">
-        <v>1.27062</v>
+        <v>1.291797</v>
       </c>
       <c r="N62">
-        <v>7.03938</v>
+        <v>7.018203000000001</v>
       </c>
       <c r="O62">
-        <v>1.9006326</v>
+        <v>1.89491481</v>
       </c>
       <c r="P62">
-        <v>5.1387474</v>
+        <v>5.12328819</v>
       </c>
       <c r="Q62">
-        <v>5.9787474</v>
+        <v>5.96328819</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.2383281523949421</v>
+        <v>0.2426285486757177</v>
       </c>
       <c r="T62">
-        <v>2.306437655910146</v>
+        <v>2.357955295247225</v>
       </c>
       <c r="U62">
         <v>0.0543</v>
@@ -6409,7 +6409,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>6.540114274920906</v>
+        <v>6.432899286807447</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6417,22 +6417,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1188049239835299</v>
+        <v>0.118495187009083</v>
       </c>
       <c r="C63">
-        <v>21.98254018892235</v>
+        <v>21.74838003553185</v>
       </c>
       <c r="D63">
-        <v>45.77254018892235</v>
+        <v>45.92838003553185</v>
       </c>
       <c r="E63">
-        <v>5.989999999999998</v>
+        <v>6.379999999999999</v>
       </c>
       <c r="F63">
-        <v>23.79</v>
+        <v>24.18</v>
       </c>
       <c r="G63">
         <v>0</v>
@@ -6453,28 +6453,28 @@
         <v>8.31</v>
       </c>
       <c r="M63">
-        <v>1.291797</v>
+        <v>1.312974</v>
       </c>
       <c r="N63">
-        <v>7.018203000000001</v>
+        <v>6.997026</v>
       </c>
       <c r="O63">
-        <v>1.89491481</v>
+        <v>1.88919702</v>
       </c>
       <c r="P63">
-        <v>5.12328819</v>
+        <v>5.10782898</v>
       </c>
       <c r="Q63">
-        <v>5.96328819</v>
+        <v>5.94782898</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.2426285486757177</v>
+        <v>0.2471552816028499</v>
       </c>
       <c r="T63">
-        <v>2.357955295247225</v>
+        <v>2.412184389286256</v>
       </c>
       <c r="U63">
         <v>0.0543</v>
@@ -6491,7 +6491,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>6.432899286807447</v>
+        <v>6.32914284669765</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6499,22 +6499,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.118495187009083</v>
+        <v>0.118185450034636</v>
       </c>
       <c r="C64">
-        <v>21.74838003553185</v>
+        <v>21.5152846701514</v>
       </c>
       <c r="D64">
-        <v>45.92838003553185</v>
+        <v>46.0852846701514</v>
       </c>
       <c r="E64">
-        <v>6.379999999999999</v>
+        <v>6.77</v>
       </c>
       <c r="F64">
-        <v>24.18</v>
+        <v>24.57</v>
       </c>
       <c r="G64">
         <v>0</v>
@@ -6535,28 +6535,28 @@
         <v>8.31</v>
       </c>
       <c r="M64">
-        <v>1.312974</v>
+        <v>1.334151</v>
       </c>
       <c r="N64">
-        <v>6.997026</v>
+        <v>6.975849</v>
       </c>
       <c r="O64">
-        <v>1.88919702</v>
+        <v>1.88347923</v>
       </c>
       <c r="P64">
-        <v>5.10782898</v>
+        <v>5.092369769999999</v>
       </c>
       <c r="Q64">
-        <v>5.94782898</v>
+        <v>5.932369769999999</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.2471552816028499</v>
+        <v>0.2519267027963136</v>
       </c>
       <c r="T64">
-        <v>2.412184389286256</v>
+        <v>2.469344785705774</v>
       </c>
       <c r="U64">
         <v>0.0543</v>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>6.32914284669765</v>
+        <v>6.228680261829433</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6581,22 +6581,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.118185450034636</v>
+        <v>0.1178757130601891</v>
       </c>
       <c r="C65">
-        <v>21.5152846701514</v>
+        <v>21.28326504306204</v>
       </c>
       <c r="D65">
-        <v>46.0852846701514</v>
+        <v>46.24326504306205</v>
       </c>
       <c r="E65">
-        <v>6.77</v>
+        <v>7.16</v>
       </c>
       <c r="F65">
-        <v>24.57</v>
+        <v>24.96</v>
       </c>
       <c r="G65">
         <v>0</v>
@@ -6617,28 +6617,28 @@
         <v>8.31</v>
       </c>
       <c r="M65">
-        <v>1.334151</v>
+        <v>1.355328</v>
       </c>
       <c r="N65">
-        <v>6.975849</v>
+        <v>6.954672</v>
       </c>
       <c r="O65">
-        <v>1.88347923</v>
+        <v>1.87776144</v>
       </c>
       <c r="P65">
-        <v>5.092369769999999</v>
+        <v>5.07691056</v>
       </c>
       <c r="Q65">
-        <v>5.932369769999999</v>
+        <v>5.91691056</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.2519267027963136</v>
+        <v>0.2569632029449697</v>
       </c>
       <c r="T65">
-        <v>2.469344785705774</v>
+        <v>2.529680759704155</v>
       </c>
       <c r="U65">
         <v>0.0543</v>
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>6.228680261829433</v>
+        <v>6.131357132738348</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6663,22 +6663,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1178757130601891</v>
+        <v>0.1180404760857421</v>
       </c>
       <c r="C66">
-        <v>21.28326504306204</v>
+        <v>20.80909358722945</v>
       </c>
       <c r="D66">
-        <v>46.24326504306205</v>
+        <v>46.15909358722945</v>
       </c>
       <c r="E66">
-        <v>7.16</v>
+        <v>7.550000000000001</v>
       </c>
       <c r="F66">
-        <v>24.96</v>
+        <v>25.35</v>
       </c>
       <c r="G66">
         <v>0</v>
@@ -6699,45 +6699,45 @@
         <v>8.31</v>
       </c>
       <c r="M66">
-        <v>1.355328</v>
+        <v>1.401855</v>
       </c>
       <c r="N66">
-        <v>6.954672</v>
+        <v>6.908145</v>
       </c>
       <c r="O66">
-        <v>1.87776144</v>
+        <v>1.86519915</v>
       </c>
       <c r="P66">
-        <v>5.07691056</v>
+        <v>5.04294585</v>
       </c>
       <c r="Q66">
-        <v>5.91691056</v>
+        <v>5.88294585</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.2569632029449697</v>
+        <v>0.2622875031021204</v>
       </c>
       <c r="T66">
-        <v>2.529680759704155</v>
+        <v>2.5934645036453</v>
       </c>
       <c r="U66">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V66">
         <v>0.27</v>
       </c>
       <c r="W66">
-        <v>0.039639</v>
+        <v>0.040369</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y66">
-        <v>6.131357132738348</v>
+        <v>5.927859871384701</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6745,22 +6745,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1180404760857421</v>
+        <v>0.1177380391112952</v>
       </c>
       <c r="C67">
-        <v>20.80909358722945</v>
+        <v>20.57383344900338</v>
       </c>
       <c r="D67">
-        <v>46.15909358722945</v>
+        <v>46.31383344900338</v>
       </c>
       <c r="E67">
-        <v>7.550000000000001</v>
+        <v>7.940000000000001</v>
       </c>
       <c r="F67">
-        <v>25.35</v>
+        <v>25.74</v>
       </c>
       <c r="G67">
         <v>0</v>
@@ -6781,28 +6781,28 @@
         <v>8.31</v>
       </c>
       <c r="M67">
-        <v>1.401855</v>
+        <v>1.423422</v>
       </c>
       <c r="N67">
-        <v>6.908145</v>
+        <v>6.886578</v>
       </c>
       <c r="O67">
-        <v>1.86519915</v>
+        <v>1.85937606</v>
       </c>
       <c r="P67">
-        <v>5.04294585</v>
+        <v>5.027201939999999</v>
       </c>
       <c r="Q67">
-        <v>5.88294585</v>
+        <v>5.867201939999999</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.2622875031021204</v>
+        <v>0.2679249973861623</v>
       </c>
       <c r="T67">
-        <v>2.5934645036453</v>
+        <v>2.661000232524159</v>
       </c>
       <c r="U67">
         <v>0.0553</v>
@@ -6819,7 +6819,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>5.927859871384701</v>
+        <v>5.838043812727356</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6827,22 +6827,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1177380391112952</v>
+        <v>0.1174356021368483</v>
       </c>
       <c r="C68">
-        <v>20.57383344900338</v>
+        <v>20.33961427420282</v>
       </c>
       <c r="D68">
-        <v>46.31383344900338</v>
+        <v>46.46961427420283</v>
       </c>
       <c r="E68">
-        <v>7.940000000000001</v>
+        <v>8.330000000000002</v>
       </c>
       <c r="F68">
-        <v>25.74</v>
+        <v>26.13</v>
       </c>
       <c r="G68">
         <v>0</v>
@@ -6863,28 +6863,28 @@
         <v>8.31</v>
       </c>
       <c r="M68">
-        <v>1.423422</v>
+        <v>1.444989</v>
       </c>
       <c r="N68">
-        <v>6.886578</v>
+        <v>6.865011</v>
       </c>
       <c r="O68">
-        <v>1.85937606</v>
+        <v>1.85355297</v>
       </c>
       <c r="P68">
-        <v>5.027201939999999</v>
+        <v>5.01145803</v>
       </c>
       <c r="Q68">
-        <v>5.867201939999999</v>
+        <v>5.85145803</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.2679249973861623</v>
+        <v>0.2739041579904493</v>
       </c>
       <c r="T68">
-        <v>2.661000232524159</v>
+        <v>2.732629035880525</v>
       </c>
       <c r="U68">
         <v>0.0553</v>
@@ -6901,7 +6901,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>5.838043812727356</v>
+        <v>5.750908830447843</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6909,22 +6909,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1174356021368483</v>
+        <v>0.1171331651624013</v>
       </c>
       <c r="C69">
-        <v>20.33961427420282</v>
+        <v>20.10644660240644</v>
       </c>
       <c r="D69">
-        <v>46.46961427420283</v>
+        <v>46.62644660240644</v>
       </c>
       <c r="E69">
-        <v>8.330000000000002</v>
+        <v>8.720000000000002</v>
       </c>
       <c r="F69">
-        <v>26.13</v>
+        <v>26.52</v>
       </c>
       <c r="G69">
         <v>0</v>
@@ -6945,28 +6945,28 @@
         <v>8.31</v>
       </c>
       <c r="M69">
-        <v>1.444989</v>
+        <v>1.466556</v>
       </c>
       <c r="N69">
-        <v>6.865011</v>
+        <v>6.843444</v>
       </c>
       <c r="O69">
-        <v>1.85355297</v>
+        <v>1.84772988</v>
       </c>
       <c r="P69">
-        <v>5.01145803</v>
+        <v>4.99571412</v>
       </c>
       <c r="Q69">
-        <v>5.85145803</v>
+        <v>5.83571412</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.2739041579904493</v>
+        <v>0.2802570161325041</v>
       </c>
       <c r="T69">
-        <v>2.732629035880525</v>
+        <v>2.808734639446665</v>
       </c>
       <c r="U69">
         <v>0.0553</v>
@@ -6983,7 +6983,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>5.750908830447843</v>
+        <v>5.666336641764787</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6991,22 +6991,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1171331651624013</v>
+        <v>0.1168307281879544</v>
       </c>
       <c r="C70">
-        <v>20.10644660240644</v>
+        <v>19.87434111595658</v>
       </c>
       <c r="D70">
-        <v>46.62644660240644</v>
+        <v>46.78434111595658</v>
       </c>
       <c r="E70">
-        <v>8.720000000000002</v>
+        <v>9.110000000000003</v>
       </c>
       <c r="F70">
-        <v>26.52</v>
+        <v>26.91</v>
       </c>
       <c r="G70">
         <v>0</v>
@@ -7027,28 +7027,28 @@
         <v>8.31</v>
       </c>
       <c r="M70">
-        <v>1.466556</v>
+        <v>1.488123</v>
       </c>
       <c r="N70">
-        <v>6.843444</v>
+        <v>6.821877000000001</v>
       </c>
       <c r="O70">
-        <v>1.84772988</v>
+        <v>1.84190679</v>
       </c>
       <c r="P70">
-        <v>4.99571412</v>
+        <v>4.97997021</v>
       </c>
       <c r="Q70">
-        <v>5.83571412</v>
+        <v>5.81997021</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.2802570161325041</v>
+        <v>0.2870197360901754</v>
       </c>
       <c r="T70">
-        <v>2.808734639446665</v>
+        <v>2.889750281952554</v>
       </c>
       <c r="U70">
         <v>0.0553</v>
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>5.666336641764787</v>
+        <v>5.584215820869646</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7073,22 +7073,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1168307281879544</v>
+        <v>0.1165282912135074</v>
       </c>
       <c r="C71">
-        <v>19.87434111595658</v>
+        <v>19.6433086423848</v>
       </c>
       <c r="D71">
-        <v>46.78434111595658</v>
+        <v>46.9433086423848</v>
       </c>
       <c r="E71">
-        <v>9.110000000000003</v>
+        <v>9.500000000000004</v>
       </c>
       <c r="F71">
-        <v>26.91</v>
+        <v>27.3</v>
       </c>
       <c r="G71">
         <v>0</v>
@@ -7109,28 +7109,28 @@
         <v>8.31</v>
       </c>
       <c r="M71">
-        <v>1.488123</v>
+        <v>1.50969</v>
       </c>
       <c r="N71">
-        <v>6.821877000000001</v>
+        <v>6.800310000000001</v>
       </c>
       <c r="O71">
-        <v>1.84190679</v>
+        <v>1.8360837</v>
       </c>
       <c r="P71">
-        <v>4.97997021</v>
+        <v>4.9642263</v>
       </c>
       <c r="Q71">
-        <v>5.81997021</v>
+        <v>5.8042263</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.2870197360901754</v>
+        <v>0.2942333040450248</v>
       </c>
       <c r="T71">
-        <v>2.889750281952554</v>
+        <v>2.976166967292171</v>
       </c>
       <c r="U71">
         <v>0.0553</v>
@@ -7147,7 +7147,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>5.584215820869646</v>
+        <v>5.504441309142936</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7155,22 +7155,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1165282912135074</v>
+        <v>0.1162258542390605</v>
       </c>
       <c r="C72">
-        <v>19.6433086423848</v>
+        <v>19.41336015688706</v>
       </c>
       <c r="D72">
-        <v>46.9433086423848</v>
+        <v>47.10336015688706</v>
       </c>
       <c r="E72">
-        <v>9.500000000000004</v>
+        <v>9.890000000000001</v>
       </c>
       <c r="F72">
-        <v>27.3</v>
+        <v>27.69</v>
       </c>
       <c r="G72">
         <v>0</v>
@@ -7191,28 +7191,28 @@
         <v>8.31</v>
       </c>
       <c r="M72">
-        <v>1.50969</v>
+        <v>1.531257</v>
       </c>
       <c r="N72">
-        <v>6.800310000000001</v>
+        <v>6.778743</v>
       </c>
       <c r="O72">
-        <v>1.8360837</v>
+        <v>1.83026061</v>
       </c>
       <c r="P72">
-        <v>4.9642263</v>
+        <v>4.948482390000001</v>
       </c>
       <c r="Q72">
-        <v>5.8042263</v>
+        <v>5.78848239</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.2942333040450248</v>
+        <v>0.3019443594450362</v>
       </c>
       <c r="T72">
-        <v>2.976166967292171</v>
+        <v>3.068543424034519</v>
       </c>
       <c r="U72">
         <v>0.0553</v>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>5.504441309142936</v>
+        <v>5.426913966760642</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7237,22 +7237,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1162258542390605</v>
+        <v>0.1159234172646136</v>
       </c>
       <c r="C73">
-        <v>19.41336015688704</v>
+        <v>19.18450678484942</v>
       </c>
       <c r="D73">
-        <v>47.10336015688704</v>
+        <v>47.26450678484942</v>
       </c>
       <c r="E73">
-        <v>9.889999999999997</v>
+        <v>10.28</v>
       </c>
       <c r="F73">
-        <v>27.69</v>
+        <v>28.08</v>
       </c>
       <c r="G73">
         <v>0</v>
@@ -7273,28 +7273,28 @@
         <v>8.31</v>
       </c>
       <c r="M73">
-        <v>1.531257</v>
+        <v>1.552824</v>
       </c>
       <c r="N73">
-        <v>6.778743</v>
+        <v>6.757176</v>
       </c>
       <c r="O73">
-        <v>1.83026061</v>
+        <v>1.82443752</v>
       </c>
       <c r="P73">
-        <v>4.948482390000001</v>
+        <v>4.93273848</v>
       </c>
       <c r="Q73">
-        <v>5.78848239</v>
+        <v>5.77273848</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.3019443594450362</v>
+        <v>0.310206204516477</v>
       </c>
       <c r="T73">
-        <v>3.068543424034518</v>
+        <v>3.167518199115606</v>
       </c>
       <c r="U73">
         <v>0.0553</v>
@@ -7311,7 +7311,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>5.426913966760642</v>
+        <v>5.351540161666744</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7319,22 +7319,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1159234172646136</v>
+        <v>0.1156209802901666</v>
       </c>
       <c r="C74">
-        <v>19.18450678484942</v>
+        <v>18.95675980442614</v>
       </c>
       <c r="D74">
-        <v>47.26450678484942</v>
+        <v>47.42675980442614</v>
       </c>
       <c r="E74">
-        <v>10.28</v>
+        <v>10.67</v>
       </c>
       <c r="F74">
-        <v>28.08</v>
+        <v>28.47</v>
       </c>
       <c r="G74">
         <v>0</v>
@@ -7355,28 +7355,28 @@
         <v>8.31</v>
       </c>
       <c r="M74">
-        <v>1.552824</v>
+        <v>1.574391</v>
       </c>
       <c r="N74">
-        <v>6.757176</v>
+        <v>6.735609</v>
       </c>
       <c r="O74">
-        <v>1.82443752</v>
+        <v>1.81861443</v>
       </c>
       <c r="P74">
-        <v>4.93273848</v>
+        <v>4.91699457</v>
       </c>
       <c r="Q74">
-        <v>5.77273848</v>
+        <v>5.75699457</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.310206204516477</v>
+        <v>0.3190800381117281</v>
       </c>
       <c r="T74">
-        <v>3.167518199115606</v>
+        <v>3.273824439017513</v>
       </c>
       <c r="U74">
         <v>0.0553</v>
@@ -7393,7 +7393,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>5.351540161666744</v>
+        <v>5.278231392328843</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7401,22 +7401,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1156209802901666</v>
+        <v>0.1153185433157197</v>
       </c>
       <c r="C75">
-        <v>18.95675980442614</v>
+        <v>18.73013064917075</v>
       </c>
       <c r="D75">
-        <v>47.42675980442614</v>
+        <v>47.59013064917075</v>
       </c>
       <c r="E75">
-        <v>10.67</v>
+        <v>11.06</v>
       </c>
       <c r="F75">
-        <v>28.47</v>
+        <v>28.86</v>
       </c>
       <c r="G75">
         <v>0</v>
@@ -7437,28 +7437,28 @@
         <v>8.31</v>
       </c>
       <c r="M75">
-        <v>1.574391</v>
+        <v>1.595958</v>
       </c>
       <c r="N75">
-        <v>6.735609</v>
+        <v>6.714042000000001</v>
       </c>
       <c r="O75">
-        <v>1.81861443</v>
+        <v>1.81279134</v>
       </c>
       <c r="P75">
-        <v>4.91699457</v>
+        <v>4.901250660000001</v>
       </c>
       <c r="Q75">
-        <v>5.75699457</v>
+        <v>5.74125066</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.3190800381117281</v>
+        <v>0.3286364742912294</v>
       </c>
       <c r="T75">
-        <v>3.273824439017513</v>
+        <v>3.3883080819888</v>
       </c>
       <c r="U75">
         <v>0.0553</v>
@@ -7475,7 +7475,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>5.278231392328843</v>
+        <v>5.206903941081157</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7483,22 +7483,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1153185433157197</v>
+        <v>0.1150161063412727</v>
       </c>
       <c r="C76">
-        <v>18.73013064917075</v>
+        <v>18.5046309107219</v>
       </c>
       <c r="D76">
-        <v>47.59013064917075</v>
+        <v>47.7546309107219</v>
       </c>
       <c r="E76">
-        <v>11.06</v>
+        <v>11.45</v>
       </c>
       <c r="F76">
-        <v>28.86</v>
+        <v>29.25</v>
       </c>
       <c r="G76">
         <v>0</v>
@@ -7519,28 +7519,28 @@
         <v>8.31</v>
       </c>
       <c r="M76">
-        <v>1.595958</v>
+        <v>1.617525</v>
       </c>
       <c r="N76">
-        <v>6.714042000000001</v>
+        <v>6.692475</v>
       </c>
       <c r="O76">
-        <v>1.81279134</v>
+        <v>1.80696825</v>
       </c>
       <c r="P76">
-        <v>4.901250660000001</v>
+        <v>4.885506749999999</v>
       </c>
       <c r="Q76">
-        <v>5.74125066</v>
+        <v>5.725506749999999</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.3286364742912294</v>
+        <v>0.3389574253650909</v>
       </c>
       <c r="T76">
-        <v>3.3883080819888</v>
+        <v>3.511950416397789</v>
       </c>
       <c r="U76">
         <v>0.0553</v>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>5.206903941081157</v>
+        <v>5.137478555200074</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7565,22 +7565,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1150161063412727</v>
+        <v>0.1147136693668258</v>
       </c>
       <c r="C77">
-        <v>18.5046309107219</v>
+        <v>18.28027234154499</v>
       </c>
       <c r="D77">
-        <v>47.7546309107219</v>
+        <v>47.92027234154499</v>
       </c>
       <c r="E77">
-        <v>11.45</v>
+        <v>11.84</v>
       </c>
       <c r="F77">
-        <v>29.25</v>
+        <v>29.64</v>
       </c>
       <c r="G77">
         <v>0</v>
@@ -7601,28 +7601,28 @@
         <v>8.31</v>
       </c>
       <c r="M77">
-        <v>1.617525</v>
+        <v>1.639092</v>
       </c>
       <c r="N77">
-        <v>6.692475</v>
+        <v>6.670908000000001</v>
       </c>
       <c r="O77">
-        <v>1.80696825</v>
+        <v>1.80114516</v>
       </c>
       <c r="P77">
-        <v>4.885506749999999</v>
+        <v>4.86976284</v>
       </c>
       <c r="Q77">
-        <v>5.725506749999999</v>
+        <v>5.70976284</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.3389574253650909</v>
+        <v>0.3501384556951074</v>
       </c>
       <c r="T77">
-        <v>3.511950416397789</v>
+        <v>3.645896278674194</v>
       </c>
       <c r="U77">
         <v>0.0553</v>
@@ -7639,7 +7639,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>5.137478555200074</v>
+        <v>5.069880153157968</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7647,22 +7647,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.1147136693668258</v>
+        <v>0.1144112323923788</v>
       </c>
       <c r="C78">
-        <v>18.28027234154499</v>
+        <v>18.05706685773111</v>
       </c>
       <c r="D78">
-        <v>47.92027234154499</v>
+        <v>48.08706685773111</v>
       </c>
       <c r="E78">
-        <v>11.84</v>
+        <v>12.23</v>
       </c>
       <c r="F78">
-        <v>29.64</v>
+        <v>30.03</v>
       </c>
       <c r="G78">
         <v>0</v>
@@ -7683,28 +7683,28 @@
         <v>8.31</v>
       </c>
       <c r="M78">
-        <v>1.639092</v>
+        <v>1.660659</v>
       </c>
       <c r="N78">
-        <v>6.670908000000001</v>
+        <v>6.649341000000001</v>
       </c>
       <c r="O78">
-        <v>1.80114516</v>
+        <v>1.79532207</v>
       </c>
       <c r="P78">
-        <v>4.86976284</v>
+        <v>4.854018930000001</v>
       </c>
       <c r="Q78">
-        <v>5.70976284</v>
+        <v>5.69401893</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.3501384556951074</v>
+        <v>0.3622917495320819</v>
       </c>
       <c r="T78">
-        <v>3.645896278674194</v>
+        <v>3.791489607235503</v>
       </c>
       <c r="U78">
         <v>0.0553</v>
@@ -7721,7 +7721,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>5.069880153157968</v>
+        <v>5.004037553766306</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7729,22 +7729,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.1144112323923788</v>
+        <v>0.1141087954179319</v>
       </c>
       <c r="C79">
-        <v>18.05706685773111</v>
+        <v>17.83502654185458</v>
       </c>
       <c r="D79">
-        <v>48.08706685773111</v>
+        <v>48.25502654185458</v>
       </c>
       <c r="E79">
-        <v>12.23</v>
+        <v>12.62</v>
       </c>
       <c r="F79">
-        <v>30.03</v>
+        <v>30.42</v>
       </c>
       <c r="G79">
         <v>0</v>
@@ -7765,28 +7765,28 @@
         <v>8.31</v>
       </c>
       <c r="M79">
-        <v>1.660659</v>
+        <v>1.682226</v>
       </c>
       <c r="N79">
-        <v>6.649341000000001</v>
+        <v>6.627774</v>
       </c>
       <c r="O79">
-        <v>1.79532207</v>
+        <v>1.78949898</v>
       </c>
       <c r="P79">
-        <v>4.854018930000001</v>
+        <v>4.83827502</v>
       </c>
       <c r="Q79">
-        <v>5.69401893</v>
+        <v>5.67827502</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.3622917495320819</v>
+        <v>0.3755498882633269</v>
       </c>
       <c r="T79">
-        <v>3.791489607235503</v>
+        <v>3.95031869293875</v>
       </c>
       <c r="U79">
         <v>0.0553</v>
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>5.004037553766306</v>
+        <v>4.939883226153917</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7811,22 +7811,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.1141087954179319</v>
+        <v>0.113806358443485</v>
       </c>
       <c r="C80">
-        <v>17.83502654185458</v>
+        <v>17.61416364589068</v>
       </c>
       <c r="D80">
-        <v>48.25502654185458</v>
+        <v>48.42416364589068</v>
       </c>
       <c r="E80">
-        <v>12.62</v>
+        <v>13.01</v>
       </c>
       <c r="F80">
-        <v>30.42</v>
+        <v>30.81</v>
       </c>
       <c r="G80">
         <v>0</v>
@@ -7847,28 +7847,28 @@
         <v>8.31</v>
       </c>
       <c r="M80">
-        <v>1.682226</v>
+        <v>1.703793</v>
       </c>
       <c r="N80">
-        <v>6.627774</v>
+        <v>6.606207</v>
       </c>
       <c r="O80">
-        <v>1.78949898</v>
+        <v>1.78367589</v>
       </c>
       <c r="P80">
-        <v>4.83827502</v>
+        <v>4.82253111</v>
       </c>
       <c r="Q80">
-        <v>5.67827502</v>
+        <v>5.66253111</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.3755498882633269</v>
+        <v>0.390070706873738</v>
       </c>
       <c r="T80">
-        <v>3.95031869293875</v>
+        <v>4.124274358232783</v>
       </c>
       <c r="U80">
         <v>0.0553</v>
@@ -7885,7 +7885,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>4.939883226153917</v>
+        <v>4.877353058734247</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7893,22 +7893,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.113806358443485</v>
+        <v>0.113503921469038</v>
       </c>
       <c r="C81">
-        <v>17.61416364589068</v>
+        <v>17.39449059419489</v>
       </c>
       <c r="D81">
-        <v>48.42416364589068</v>
+        <v>48.59449059419489</v>
       </c>
       <c r="E81">
-        <v>13.01</v>
+        <v>13.4</v>
       </c>
       <c r="F81">
-        <v>30.81</v>
+        <v>31.2</v>
       </c>
       <c r="G81">
         <v>0</v>
@@ -7929,28 +7929,28 @@
         <v>8.31</v>
       </c>
       <c r="M81">
-        <v>1.703793</v>
+        <v>1.72536</v>
       </c>
       <c r="N81">
-        <v>6.606207</v>
+        <v>6.58464</v>
       </c>
       <c r="O81">
-        <v>1.78367589</v>
+        <v>1.7778528</v>
       </c>
       <c r="P81">
-        <v>4.82253111</v>
+        <v>4.8067872</v>
       </c>
       <c r="Q81">
-        <v>5.66253111</v>
+        <v>5.6467872</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.390070706873738</v>
+        <v>0.4060436073451901</v>
       </c>
       <c r="T81">
-        <v>4.124274358232783</v>
+        <v>4.315625590056218</v>
       </c>
       <c r="U81">
         <v>0.0553</v>
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>4.877353058734247</v>
+        <v>4.816386145500069</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7975,22 +7975,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.113503921469038</v>
+        <v>0.1132014844945911</v>
       </c>
       <c r="C82">
-        <v>17.39449059419489</v>
+        <v>17.17601998654516</v>
       </c>
       <c r="D82">
-        <v>48.59449059419489</v>
+        <v>48.76601998654516</v>
       </c>
       <c r="E82">
-        <v>13.4</v>
+        <v>13.79</v>
       </c>
       <c r="F82">
-        <v>31.2</v>
+        <v>31.59</v>
       </c>
       <c r="G82">
         <v>0</v>
@@ -8011,28 +8011,28 @@
         <v>8.31</v>
       </c>
       <c r="M82">
-        <v>1.72536</v>
+        <v>1.746927</v>
       </c>
       <c r="N82">
-        <v>6.58464</v>
+        <v>6.563073</v>
       </c>
       <c r="O82">
-        <v>1.7778528</v>
+        <v>1.77202971</v>
       </c>
       <c r="P82">
-        <v>4.8067872</v>
+        <v>4.79104329</v>
       </c>
       <c r="Q82">
-        <v>5.6467872</v>
+        <v>5.63104329</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.4060436073451901</v>
+        <v>0.4236978657610057</v>
       </c>
       <c r="T82">
-        <v>4.315625590056218</v>
+        <v>4.527119056808435</v>
       </c>
       <c r="U82">
         <v>0.0553</v>
@@ -8049,7 +8049,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>4.816386145500069</v>
+        <v>4.756924588148216</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8057,22 +8057,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1132014844945911</v>
+        <v>0.1128990475201441</v>
       </c>
       <c r="C83">
-        <v>17.17601998654516</v>
+        <v>16.95876460124902</v>
       </c>
       <c r="D83">
-        <v>48.76601998654516</v>
+        <v>48.93876460124903</v>
       </c>
       <c r="E83">
-        <v>13.79</v>
+        <v>14.18</v>
       </c>
       <c r="F83">
-        <v>31.59</v>
+        <v>31.98</v>
       </c>
       <c r="G83">
         <v>0</v>
@@ -8093,28 +8093,28 @@
         <v>8.31</v>
       </c>
       <c r="M83">
-        <v>1.746927</v>
+        <v>1.768494</v>
       </c>
       <c r="N83">
-        <v>6.563073</v>
+        <v>6.541506</v>
       </c>
       <c r="O83">
-        <v>1.77202971</v>
+        <v>1.76620662</v>
       </c>
       <c r="P83">
-        <v>4.79104329</v>
+        <v>4.77529938</v>
       </c>
       <c r="Q83">
-        <v>5.63104329</v>
+        <v>5.61529938</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.4236978657610057</v>
+        <v>0.4433137084452453</v>
       </c>
       <c r="T83">
-        <v>4.527119056808435</v>
+        <v>4.762111797644234</v>
       </c>
       <c r="U83">
         <v>0.0553</v>
@@ -8131,7 +8131,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>4.756924588148216</v>
+        <v>4.698913312682994</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8139,22 +8139,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.1128990475201441</v>
+        <v>0.1125966105456972</v>
       </c>
       <c r="C84">
-        <v>16.95876460124902</v>
+        <v>16.74273739831684</v>
       </c>
       <c r="D84">
-        <v>48.93876460124903</v>
+        <v>49.11273739831685</v>
       </c>
       <c r="E84">
-        <v>14.18</v>
+        <v>14.57</v>
       </c>
       <c r="F84">
-        <v>31.98</v>
+        <v>32.37</v>
       </c>
       <c r="G84">
         <v>0</v>
@@ -8175,28 +8175,28 @@
         <v>8.31</v>
       </c>
       <c r="M84">
-        <v>1.768494</v>
+        <v>1.790061</v>
       </c>
       <c r="N84">
-        <v>6.541506</v>
+        <v>6.519939</v>
       </c>
       <c r="O84">
-        <v>1.76620662</v>
+        <v>1.76038353</v>
       </c>
       <c r="P84">
-        <v>4.77529938</v>
+        <v>4.75955547</v>
       </c>
       <c r="Q84">
-        <v>5.61529938</v>
+        <v>5.599555469999999</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.4433137084452453</v>
+        <v>0.4652372973276306</v>
       </c>
       <c r="T84">
-        <v>4.762111797644234</v>
+        <v>5.024750743284244</v>
       </c>
       <c r="U84">
         <v>0.0553</v>
@@ -8213,7 +8213,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>4.698913312682994</v>
+        <v>4.642299899277175</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8221,22 +8221,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.1125966105456972</v>
+        <v>0.1122941735712503</v>
       </c>
       <c r="C85">
-        <v>16.74273739831684</v>
+        <v>16.52795152270298</v>
       </c>
       <c r="D85">
-        <v>49.11273739831685</v>
+        <v>49.28795152270299</v>
       </c>
       <c r="E85">
-        <v>14.57</v>
+        <v>14.96</v>
       </c>
       <c r="F85">
-        <v>32.37</v>
+        <v>32.76000000000001</v>
       </c>
       <c r="G85">
         <v>0</v>
@@ -8257,28 +8257,28 @@
         <v>8.31</v>
       </c>
       <c r="M85">
-        <v>1.790061</v>
+        <v>1.811628</v>
       </c>
       <c r="N85">
-        <v>6.519939</v>
+        <v>6.498372</v>
       </c>
       <c r="O85">
-        <v>1.76038353</v>
+        <v>1.75456044</v>
       </c>
       <c r="P85">
-        <v>4.75955547</v>
+        <v>4.743811559999999</v>
       </c>
       <c r="Q85">
-        <v>5.599555469999999</v>
+        <v>5.583811559999999</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.4652372973276306</v>
+        <v>0.4899013348203143</v>
       </c>
       <c r="T85">
-        <v>5.024750743284244</v>
+        <v>5.320219557129255</v>
       </c>
       <c r="U85">
         <v>0.0553</v>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>4.642299899277175</v>
+        <v>4.58703442428578</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8303,22 +8303,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.1122941735712503</v>
+        <v>0.1119917365968033</v>
       </c>
       <c r="C86">
-        <v>16.52795152270299</v>
+        <v>16.31442030761673</v>
       </c>
       <c r="D86">
-        <v>49.28795152270299</v>
+        <v>49.46442030761673</v>
       </c>
       <c r="E86">
-        <v>14.96</v>
+        <v>15.35</v>
       </c>
       <c r="F86">
-        <v>32.76</v>
+        <v>33.15</v>
       </c>
       <c r="G86">
         <v>0</v>
@@ -8339,28 +8339,28 @@
         <v>8.31</v>
       </c>
       <c r="M86">
-        <v>1.811628</v>
+        <v>1.833195</v>
       </c>
       <c r="N86">
-        <v>6.498372000000001</v>
+        <v>6.476805000000001</v>
       </c>
       <c r="O86">
-        <v>1.75456044</v>
+        <v>1.74873735</v>
       </c>
       <c r="P86">
-        <v>4.74381156</v>
+        <v>4.72806765</v>
       </c>
       <c r="Q86">
-        <v>5.58381156</v>
+        <v>5.56806765</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.4899013348203139</v>
+        <v>0.5178539106453552</v>
       </c>
       <c r="T86">
-        <v>5.320219557129252</v>
+        <v>5.655084212820263</v>
       </c>
       <c r="U86">
         <v>0.0553</v>
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>4.587034424285781</v>
+        <v>4.533069313411831</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8385,22 +8385,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.1119917365968033</v>
+        <v>0.1132587996223564</v>
       </c>
       <c r="C87">
-        <v>16.31442030761673</v>
+        <v>15.19342034770634</v>
       </c>
       <c r="D87">
-        <v>49.46442030761673</v>
+        <v>48.73342034770634</v>
       </c>
       <c r="E87">
-        <v>15.35</v>
+        <v>15.74</v>
       </c>
       <c r="F87">
-        <v>33.15</v>
+        <v>33.54</v>
       </c>
       <c r="G87">
         <v>0</v>
@@ -8421,45 +8421,45 @@
         <v>8.31</v>
       </c>
       <c r="M87">
-        <v>1.833195</v>
+        <v>1.938612</v>
       </c>
       <c r="N87">
-        <v>6.476805000000001</v>
+        <v>6.371388</v>
       </c>
       <c r="O87">
-        <v>1.74873735</v>
+        <v>1.72027476</v>
       </c>
       <c r="P87">
-        <v>4.72806765</v>
+        <v>4.65111324</v>
       </c>
       <c r="Q87">
-        <v>5.56806765</v>
+        <v>5.49111324</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.5178539106453552</v>
+        <v>0.5497997115882596</v>
       </c>
       <c r="T87">
-        <v>5.655084212820263</v>
+        <v>6.037786676467134</v>
       </c>
       <c r="U87">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V87">
         <v>0.27</v>
       </c>
       <c r="W87">
-        <v>0.040369</v>
+        <v>0.042194</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y87">
-        <v>4.533069313411831</v>
+        <v>4.286572042265291</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8467,22 +8467,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.1132587996223564</v>
+        <v>0.1129746126479094</v>
       </c>
       <c r="C88">
-        <v>15.19342034770634</v>
+        <v>14.96548905730038</v>
       </c>
       <c r="D88">
-        <v>48.73342034770634</v>
+        <v>48.89548905730038</v>
       </c>
       <c r="E88">
-        <v>15.74</v>
+        <v>16.13</v>
       </c>
       <c r="F88">
-        <v>33.54</v>
+        <v>33.93</v>
       </c>
       <c r="G88">
         <v>0</v>
@@ -8503,28 +8503,28 @@
         <v>8.31</v>
       </c>
       <c r="M88">
-        <v>1.938612</v>
+        <v>1.961154</v>
       </c>
       <c r="N88">
-        <v>6.371388</v>
+        <v>6.348846</v>
       </c>
       <c r="O88">
-        <v>1.72027476</v>
+        <v>1.71418842</v>
       </c>
       <c r="P88">
-        <v>4.65111324</v>
+        <v>4.63465758</v>
       </c>
       <c r="Q88">
-        <v>5.49111324</v>
+        <v>5.47465758</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.5497997115882596</v>
+        <v>0.5866602511377647</v>
       </c>
       <c r="T88">
-        <v>6.037786676467134</v>
+        <v>6.479366442213523</v>
       </c>
       <c r="U88">
         <v>0.0578</v>
@@ -8541,7 +8541,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>4.286572042265291</v>
+        <v>4.237301099250747</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8549,22 +8549,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.1129746126479094</v>
+        <v>0.1126904256734625</v>
       </c>
       <c r="C89">
-        <v>14.96548905730038</v>
+        <v>14.73863932076287</v>
       </c>
       <c r="D89">
-        <v>48.89548905730038</v>
+        <v>49.05863932076287</v>
       </c>
       <c r="E89">
-        <v>16.13</v>
+        <v>16.52</v>
       </c>
       <c r="F89">
-        <v>33.93</v>
+        <v>34.32</v>
       </c>
       <c r="G89">
         <v>0</v>
@@ -8585,28 +8585,28 @@
         <v>8.31</v>
       </c>
       <c r="M89">
-        <v>1.961154</v>
+        <v>1.983696</v>
       </c>
       <c r="N89">
-        <v>6.348846</v>
+        <v>6.326304</v>
       </c>
       <c r="O89">
-        <v>1.71418842</v>
+        <v>1.70810208</v>
       </c>
       <c r="P89">
-        <v>4.63465758</v>
+        <v>4.618201920000001</v>
       </c>
       <c r="Q89">
-        <v>5.47465758</v>
+        <v>5.45820192</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.5866602511377647</v>
+        <v>0.6296642139455205</v>
       </c>
       <c r="T89">
-        <v>6.479366442213523</v>
+        <v>6.994542835584311</v>
       </c>
       <c r="U89">
         <v>0.0578</v>
@@ -8623,7 +8623,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>4.237301099250747</v>
+        <v>4.189149950395626</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8631,22 +8631,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.1126904256734625</v>
+        <v>0.1124062386990155</v>
       </c>
       <c r="C90">
-        <v>14.73863932076287</v>
+        <v>14.51288200084753</v>
       </c>
       <c r="D90">
-        <v>49.05863932076287</v>
+        <v>49.22288200084753</v>
       </c>
       <c r="E90">
-        <v>16.52</v>
+        <v>16.91</v>
       </c>
       <c r="F90">
-        <v>34.32</v>
+        <v>34.71</v>
       </c>
       <c r="G90">
         <v>0</v>
@@ -8667,28 +8667,28 @@
         <v>8.31</v>
       </c>
       <c r="M90">
-        <v>1.983696</v>
+        <v>2.006238</v>
       </c>
       <c r="N90">
-        <v>6.326304</v>
+        <v>6.303762000000001</v>
       </c>
       <c r="O90">
-        <v>1.70810208</v>
+        <v>1.70201574</v>
       </c>
       <c r="P90">
-        <v>4.618201920000001</v>
+        <v>4.601746260000001</v>
       </c>
       <c r="Q90">
-        <v>5.45820192</v>
+        <v>5.44174626</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.6296642139455205</v>
+        <v>0.6804870790819594</v>
       </c>
       <c r="T90">
-        <v>6.994542835584311</v>
+        <v>7.603387664113424</v>
       </c>
       <c r="U90">
         <v>0.0578</v>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>4.189149950395626</v>
+        <v>4.142080849829382</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8713,22 +8713,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.1124062386990155</v>
+        <v>0.1121220517245686</v>
       </c>
       <c r="C91">
-        <v>14.51288200084753</v>
+        <v>14.28822810626576</v>
       </c>
       <c r="D91">
-        <v>49.22288200084753</v>
+        <v>49.38822810626576</v>
       </c>
       <c r="E91">
-        <v>16.91</v>
+        <v>17.3</v>
       </c>
       <c r="F91">
-        <v>34.71</v>
+        <v>35.1</v>
       </c>
       <c r="G91">
         <v>0</v>
@@ -8749,28 +8749,28 @@
         <v>8.31</v>
       </c>
       <c r="M91">
-        <v>2.006238</v>
+        <v>2.02878</v>
       </c>
       <c r="N91">
-        <v>6.303762000000001</v>
+        <v>6.28122</v>
       </c>
       <c r="O91">
-        <v>1.70201574</v>
+        <v>1.6959294</v>
       </c>
       <c r="P91">
-        <v>4.601746260000001</v>
+        <v>4.5852906</v>
       </c>
       <c r="Q91">
-        <v>5.44174626</v>
+        <v>5.4252906</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.6804870790819594</v>
+        <v>0.7414745172456859</v>
       </c>
       <c r="T91">
-        <v>7.603387664113424</v>
+        <v>8.334001458348359</v>
       </c>
       <c r="U91">
         <v>0.0578</v>
@@ -8787,7 +8787,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>4.142080849829382</v>
+        <v>4.096057729275723</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8795,22 +8795,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.1121220517245686</v>
+        <v>0.1118378647501217</v>
       </c>
       <c r="C92">
-        <v>14.28822810626576</v>
+        <v>14.06468879414629</v>
       </c>
       <c r="D92">
-        <v>49.38822810626576</v>
+        <v>49.55468879414629</v>
       </c>
       <c r="E92">
-        <v>17.3</v>
+        <v>17.69</v>
       </c>
       <c r="F92">
-        <v>35.1</v>
+        <v>35.49</v>
       </c>
       <c r="G92">
         <v>0</v>
@@ -8831,28 +8831,28 @@
         <v>8.31</v>
       </c>
       <c r="M92">
-        <v>2.02878</v>
+        <v>2.051322</v>
       </c>
       <c r="N92">
-        <v>6.28122</v>
+        <v>6.258678</v>
       </c>
       <c r="O92">
-        <v>1.6959294</v>
+        <v>1.68984306</v>
       </c>
       <c r="P92">
-        <v>4.5852906</v>
+        <v>4.568834939999999</v>
       </c>
       <c r="Q92">
-        <v>5.4252906</v>
+        <v>5.408834939999999</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.7414745172456859</v>
+        <v>0.8160147194457964</v>
       </c>
       <c r="T92">
-        <v>8.334001458348359</v>
+        <v>9.226973873524393</v>
       </c>
       <c r="U92">
         <v>0.0578</v>
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>4.096057729275723</v>
+        <v>4.051046105877088</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8877,22 +8877,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.1118378647501217</v>
+        <v>0.1115536777756747</v>
       </c>
       <c r="C93">
-        <v>14.06468879414629</v>
+        <v>13.84227537254491</v>
       </c>
       <c r="D93">
-        <v>49.55468879414629</v>
+        <v>49.72227537254491</v>
       </c>
       <c r="E93">
-        <v>17.69</v>
+        <v>18.08</v>
       </c>
       <c r="F93">
-        <v>35.49</v>
+        <v>35.88</v>
       </c>
       <c r="G93">
         <v>0</v>
@@ -8913,28 +8913,28 @@
         <v>8.31</v>
       </c>
       <c r="M93">
-        <v>2.051322</v>
+        <v>2.073864</v>
       </c>
       <c r="N93">
-        <v>6.258678</v>
+        <v>6.236136</v>
       </c>
       <c r="O93">
-        <v>1.68984306</v>
+        <v>1.68375672</v>
       </c>
       <c r="P93">
-        <v>4.568834939999999</v>
+        <v>4.55237928</v>
       </c>
       <c r="Q93">
-        <v>5.408834939999999</v>
+        <v>5.39237928</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.8160147194457964</v>
+        <v>0.9091899721959342</v>
       </c>
       <c r="T93">
-        <v>9.226973873524393</v>
+        <v>10.34318939249443</v>
       </c>
       <c r="U93">
         <v>0.0578</v>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>4.051046105877088</v>
+        <v>4.007012996030598</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8959,22 +8959,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.1115536777756747</v>
+        <v>0.1136456408012278</v>
       </c>
       <c r="C94">
-        <v>13.84227537254491</v>
+        <v>12.24452792934856</v>
       </c>
       <c r="D94">
-        <v>49.72227537254491</v>
+        <v>48.51452792934856</v>
       </c>
       <c r="E94">
-        <v>18.08</v>
+        <v>18.47</v>
       </c>
       <c r="F94">
-        <v>35.88</v>
+        <v>36.27</v>
       </c>
       <c r="G94">
         <v>0</v>
@@ -8995,45 +8995,45 @@
         <v>8.31</v>
       </c>
       <c r="M94">
-        <v>2.073864</v>
+        <v>2.223351</v>
       </c>
       <c r="N94">
-        <v>6.236136</v>
+        <v>6.086649</v>
       </c>
       <c r="O94">
-        <v>1.68375672</v>
+        <v>1.64339523</v>
       </c>
       <c r="P94">
-        <v>4.55237928</v>
+        <v>4.44325377</v>
       </c>
       <c r="Q94">
-        <v>5.39237928</v>
+        <v>5.28325377</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.9091899721959342</v>
+        <v>1.028986725731826</v>
       </c>
       <c r="T94">
-        <v>10.34318939249443</v>
+        <v>11.7783236311702</v>
       </c>
       <c r="U94">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V94">
         <v>0.27</v>
       </c>
       <c r="W94">
-        <v>0.042194</v>
+        <v>0.044749</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y94">
-        <v>4.007012996030598</v>
+        <v>3.737601485325529</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9041,22 +9041,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.1136456408012278</v>
+        <v>0.1133870038267808</v>
       </c>
       <c r="C95">
-        <v>12.24452792934856</v>
+        <v>12.00065804124551</v>
       </c>
       <c r="D95">
-        <v>48.51452792934856</v>
+        <v>48.66065804124551</v>
       </c>
       <c r="E95">
-        <v>18.47</v>
+        <v>18.86</v>
       </c>
       <c r="F95">
-        <v>36.27</v>
+        <v>36.66</v>
       </c>
       <c r="G95">
         <v>0</v>
@@ -9077,28 +9077,28 @@
         <v>8.31</v>
       </c>
       <c r="M95">
-        <v>2.223351</v>
+        <v>2.247258</v>
       </c>
       <c r="N95">
-        <v>6.086649</v>
+        <v>6.062742</v>
       </c>
       <c r="O95">
-        <v>1.64339523</v>
+        <v>1.63694034</v>
       </c>
       <c r="P95">
-        <v>4.44325377</v>
+        <v>4.425801659999999</v>
       </c>
       <c r="Q95">
-        <v>5.28325377</v>
+        <v>5.265801659999999</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>1.028986725731826</v>
+        <v>1.188715730446348</v>
       </c>
       <c r="T95">
-        <v>11.7783236311702</v>
+        <v>13.69183594940456</v>
       </c>
       <c r="U95">
         <v>0.0613</v>
@@ -9115,7 +9115,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>3.737601485325529</v>
+        <v>3.697839767396534</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9123,22 +9123,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.1133870038267808</v>
+        <v>0.1131283668523339</v>
       </c>
       <c r="C96">
-        <v>12.00065804124551</v>
+        <v>11.75767112676017</v>
       </c>
       <c r="D96">
-        <v>48.66065804124551</v>
+        <v>48.80767112676018</v>
       </c>
       <c r="E96">
-        <v>18.86</v>
+        <v>19.25</v>
       </c>
       <c r="F96">
-        <v>36.66</v>
+        <v>37.05</v>
       </c>
       <c r="G96">
         <v>0</v>
@@ -9159,28 +9159,28 @@
         <v>8.31</v>
       </c>
       <c r="M96">
-        <v>2.247258</v>
+        <v>2.271165</v>
       </c>
       <c r="N96">
-        <v>6.062742</v>
+        <v>6.038835000000001</v>
       </c>
       <c r="O96">
-        <v>1.63694034</v>
+        <v>1.63048545</v>
       </c>
       <c r="P96">
-        <v>4.425801659999999</v>
+        <v>4.408349550000001</v>
       </c>
       <c r="Q96">
-        <v>5.265801659999999</v>
+        <v>5.24834955</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>1.188715730446348</v>
+        <v>1.41233633704668</v>
       </c>
       <c r="T96">
-        <v>13.69183594940456</v>
+        <v>16.37075319493266</v>
       </c>
       <c r="U96">
         <v>0.0613</v>
@@ -9197,7 +9197,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>3.697839767396534</v>
+        <v>3.658915138266044</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9205,22 +9205,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.1131283668523339</v>
+        <v>0.1128697298778869</v>
       </c>
       <c r="C97">
-        <v>11.75767112676017</v>
+        <v>11.51557521303693</v>
       </c>
       <c r="D97">
-        <v>48.80767112676018</v>
+        <v>48.95557521303694</v>
       </c>
       <c r="E97">
-        <v>19.25</v>
+        <v>19.64</v>
       </c>
       <c r="F97">
-        <v>37.05</v>
+        <v>37.44</v>
       </c>
       <c r="G97">
         <v>0</v>
@@ -9241,28 +9241,28 @@
         <v>8.31</v>
       </c>
       <c r="M97">
-        <v>2.271165</v>
+        <v>2.295072</v>
       </c>
       <c r="N97">
-        <v>6.038835000000001</v>
+        <v>6.014928</v>
       </c>
       <c r="O97">
-        <v>1.63048545</v>
+        <v>1.62403056</v>
       </c>
       <c r="P97">
-        <v>4.408349550000001</v>
+        <v>4.39089744</v>
       </c>
       <c r="Q97">
-        <v>5.24834955</v>
+        <v>5.23089744</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.41233633704668</v>
+        <v>1.747767246947176</v>
       </c>
       <c r="T97">
-        <v>16.37075319493266</v>
+        <v>20.38912906322481</v>
       </c>
       <c r="U97">
         <v>0.0613</v>
@@ -9279,7 +9279,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>3.658915138266044</v>
+        <v>3.620801438909106</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9287,22 +9287,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.1128697298778869</v>
+        <v>0.11261109290344</v>
       </c>
       <c r="C98">
-        <v>11.51557521303694</v>
+        <v>11.27437842481581</v>
       </c>
       <c r="D98">
-        <v>48.95557521303694</v>
+        <v>49.10437842481581</v>
       </c>
       <c r="E98">
-        <v>19.64</v>
+        <v>20.03</v>
       </c>
       <c r="F98">
-        <v>37.44</v>
+        <v>37.83</v>
       </c>
       <c r="G98">
         <v>0</v>
@@ -9323,28 +9323,28 @@
         <v>8.31</v>
       </c>
       <c r="M98">
-        <v>2.295072</v>
+        <v>2.318979</v>
       </c>
       <c r="N98">
-        <v>6.014928000000001</v>
+        <v>5.991021</v>
       </c>
       <c r="O98">
-        <v>1.62403056</v>
+        <v>1.61757567</v>
       </c>
       <c r="P98">
-        <v>4.390897440000001</v>
+        <v>4.37344533</v>
       </c>
       <c r="Q98">
-        <v>5.230897440000001</v>
+        <v>5.21344533</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.747767246947172</v>
+        <v>2.306818763447998</v>
       </c>
       <c r="T98">
-        <v>20.38912906322476</v>
+        <v>27.08642217704499</v>
       </c>
       <c r="U98">
         <v>0.0613</v>
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>3.620801438909107</v>
+        <v>3.583473589023445</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9369,22 +9369,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.11261109290344</v>
+        <v>0.112352455928993</v>
       </c>
       <c r="C99">
-        <v>11.27437842481581</v>
+        <v>11.03408898592055</v>
       </c>
       <c r="D99">
-        <v>49.10437842481581</v>
+        <v>49.25408898592055</v>
       </c>
       <c r="E99">
-        <v>20.03</v>
+        <v>20.42</v>
       </c>
       <c r="F99">
-        <v>37.83</v>
+        <v>38.22</v>
       </c>
       <c r="G99">
         <v>0</v>
@@ -9405,28 +9405,28 @@
         <v>8.31</v>
       </c>
       <c r="M99">
-        <v>2.318979</v>
+        <v>2.342886</v>
       </c>
       <c r="N99">
-        <v>5.991021</v>
+        <v>5.967114</v>
       </c>
       <c r="O99">
-        <v>1.61757567</v>
+        <v>1.61112078</v>
       </c>
       <c r="P99">
-        <v>4.37344533</v>
+        <v>4.35599322</v>
       </c>
       <c r="Q99">
-        <v>5.21344533</v>
+        <v>5.19599322</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>2.306818763447998</v>
+        <v>3.424921796449649</v>
       </c>
       <c r="T99">
-        <v>27.08642217704499</v>
+        <v>40.48100840468545</v>
       </c>
       <c r="U99">
         <v>0.0613</v>
@@ -9443,7 +9443,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>3.583473589023445</v>
+        <v>3.546907531992594</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9451,22 +9451,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.112352455928993</v>
+        <v>0.1120938189545461</v>
       </c>
       <c r="C100">
-        <v>11.03408898592055</v>
+        <v>10.79471522077341</v>
       </c>
       <c r="D100">
-        <v>49.25408898592055</v>
+        <v>49.40471522077341</v>
       </c>
       <c r="E100">
-        <v>20.42</v>
+        <v>20.81</v>
       </c>
       <c r="F100">
-        <v>38.22</v>
+        <v>38.61</v>
       </c>
       <c r="G100">
         <v>0</v>
@@ -9487,28 +9487,28 @@
         <v>8.31</v>
       </c>
       <c r="M100">
-        <v>2.342886</v>
+        <v>2.366793</v>
       </c>
       <c r="N100">
-        <v>5.967114</v>
+        <v>5.943207000000001</v>
       </c>
       <c r="O100">
-        <v>1.61112078</v>
+        <v>1.60466589</v>
       </c>
       <c r="P100">
-        <v>4.35599322</v>
+        <v>4.33854111</v>
       </c>
       <c r="Q100">
-        <v>5.19599322</v>
+        <v>5.17854111</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>3.424921796449649</v>
+        <v>6.779230895454606</v>
       </c>
       <c r="T100">
-        <v>40.48100840468545</v>
+        <v>80.66476708760683</v>
       </c>
       <c r="U100">
         <v>0.0613</v>
@@ -9525,91 +9525,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>3.546907531992594</v>
+        <v>3.511080183184588</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.1120938189545461</v>
-      </c>
-      <c r="C101">
-        <v>10.79471522077341</v>
-      </c>
-      <c r="D101">
-        <v>49.40471522077341</v>
-      </c>
-      <c r="E101">
-        <v>20.81</v>
-      </c>
-      <c r="F101">
-        <v>38.61</v>
-      </c>
-      <c r="G101">
-        <v>0</v>
-      </c>
-      <c r="H101">
-        <v>21.2</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>9.15</v>
-      </c>
-      <c r="K101">
-        <v>0.8399999999999999</v>
-      </c>
-      <c r="L101">
-        <v>8.31</v>
-      </c>
-      <c r="M101">
-        <v>2.366793</v>
-      </c>
-      <c r="N101">
-        <v>5.943207000000001</v>
-      </c>
-      <c r="O101">
-        <v>1.60466589</v>
-      </c>
-      <c r="P101">
-        <v>4.33854111</v>
-      </c>
-      <c r="Q101">
-        <v>5.17854111</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>6.779230895454606</v>
-      </c>
-      <c r="T101">
-        <v>80.66476708760683</v>
-      </c>
-      <c r="U101">
-        <v>0.0613</v>
-      </c>
-      <c r="V101">
-        <v>0.27</v>
-      </c>
-      <c r="W101">
-        <v>0.044749</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>Ba1/BB+</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>3.511080183184588</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
